--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（806段落130表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（843段落137表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>806段落 130表</t>
+          <t>843段落 137表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（806段落130表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（843段落137表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -3595,17 +3595,17 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
+          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -3633,34 +3633,34 @@
       <c r="A70" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>44 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -3678,34 +3678,34 @@
       <c r="A71" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>44 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -3730,27 +3730,27 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3758,9 +3758,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I72" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3775,27 +3775,27 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -3813,34 +3813,34 @@
       <c r="A74" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -3848,9 +3848,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I74" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3865,27 +3865,27 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3893,9 +3893,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3910,27 +3910,27 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -3938,9 +3938,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3955,27 +3955,27 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -4000,27 +4000,27 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -4090,17 +4090,17 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -4135,27 +4135,27 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -4180,27 +4180,27 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -4208,9 +4208,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I82" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4225,27 +4225,27 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -4270,27 +4270,27 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
@@ -4315,17 +4315,17 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -4360,27 +4360,27 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -4388,9 +4388,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4405,27 +4405,27 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
@@ -4433,9 +4433,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I87" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4450,27 +4450,27 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -4495,27 +4495,27 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -4540,27 +4540,27 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -4578,44 +4578,44 @@
       <c r="A91" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I91" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4630,32 +4630,32 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I92" s="12" t="inlineStr">
@@ -4675,27 +4675,27 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
@@ -4703,9 +4703,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I93" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I93" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4713,34 +4713,34 @@
       <c r="A94" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -4748,9 +4748,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4765,17 +4765,17 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -4793,9 +4793,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I95" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4803,44 +4803,44 @@
       <c r="A96" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H96" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I96" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I96" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4855,27 +4855,27 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H97" s="18" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H98" s="18" t="inlineStr">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -4990,95 +4990,119 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H100" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I100" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="52" customHeight="1">
+      <c r="A101" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="D101" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E101" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="F101" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H100" s="18" t="inlineStr">
+      <c r="H101" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I100" s="18" t="inlineStr">
+      <c r="I101" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="19" t="inlineStr">
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="28" customHeight="1">
-      <c r="A103" s="3" t="inlineStr">
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr"/>
-      <c r="E103" s="3" t="inlineStr"/>
-      <c r="F103" s="3" t="inlineStr"/>
-      <c r="G103" s="3" t="inlineStr"/>
-      <c r="H103" s="3" t="inlineStr"/>
-      <c r="I103" s="3" t="inlineStr"/>
-    </row>
-    <row r="104" ht="32" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr"/>
+      <c r="E104" s="3" t="inlineStr"/>
+      <c r="F104" s="3" t="inlineStr"/>
+      <c r="G104" s="3" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D104" s="20" t="n"/>
-      <c r="E104" s="20" t="n"/>
-      <c r="F104" s="20" t="n"/>
-      <c r="G104" s="20" t="n"/>
-      <c r="H104" s="20" t="n"/>
-      <c r="I104" s="21" t="n"/>
-    </row>
-    <row r="105" ht="32" customHeight="1">
-      <c r="A105" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B105" s="6" t="n">
@@ -5086,7 +5110,7 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D105" s="20" t="n"/>
@@ -5097,17 +5121,17 @@
       <c r="I105" s="21" t="n"/>
     </row>
     <row r="106" ht="32" customHeight="1">
-      <c r="A106" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B106" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D106" s="20" t="n"/>
@@ -5118,17 +5142,17 @@
       <c r="I106" s="21" t="n"/>
     </row>
     <row r="107" ht="32" customHeight="1">
-      <c r="A107" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A107" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D107" s="20" t="n"/>
@@ -5139,17 +5163,17 @@
       <c r="I107" s="21" t="n"/>
     </row>
     <row r="108" ht="32" customHeight="1">
-      <c r="A108" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A108" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B108" s="6" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D108" s="20" t="n"/>
@@ -5160,17 +5184,17 @@
       <c r="I108" s="21" t="n"/>
     </row>
     <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D109" s="20" t="n"/>
@@ -5181,17 +5205,17 @@
       <c r="I109" s="21" t="n"/>
     </row>
     <row r="110" ht="32" customHeight="1">
-      <c r="A110" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B110" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D110" s="20" t="n"/>
@@ -5202,17 +5226,17 @@
       <c r="I110" s="21" t="n"/>
     </row>
     <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D111" s="20" t="n"/>
@@ -5222,18 +5246,18 @@
       <c r="H111" s="20" t="n"/>
       <c r="I111" s="21" t="n"/>
     </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B112" s="22" t="n">
-        <v>96</v>
-      </c>
-      <c r="C112" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの91件、別スコープ5件</t>
+    <row r="112" ht="32" customHeight="1">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D112" s="20" t="n"/>
@@ -5243,8 +5267,29 @@
       <c r="H112" s="20" t="n"/>
       <c r="I112" s="21" t="n"/>
     </row>
-    <row r="114" ht="100" customHeight="1">
-      <c r="A114" s="23" t="inlineStr">
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B113" s="22" t="n">
+        <v>97</v>
+      </c>
+      <c r="C113" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの92件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D113" s="20" t="n"/>
+      <c r="E113" s="20" t="n"/>
+      <c r="F113" s="20" t="n"/>
+      <c r="G113" s="20" t="n"/>
+      <c r="H113" s="20" t="n"/>
+      <c r="I113" s="21" t="n"/>
+    </row>
+    <row r="115" ht="100" customHeight="1">
+      <c r="A115" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -5255,14 +5300,14 @@
     <mergeCell ref="C111:I111"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C110:I110"/>
-    <mergeCell ref="A114:H114"/>
+    <mergeCell ref="A103:I103"/>
     <mergeCell ref="C106:I106"/>
     <mergeCell ref="C105:I105"/>
-    <mergeCell ref="A102:I102"/>
+    <mergeCell ref="C113:I113"/>
+    <mergeCell ref="A115:H115"/>
     <mergeCell ref="C109:I109"/>
     <mergeCell ref="C112:I112"/>
     <mergeCell ref="C108:I108"/>
-    <mergeCell ref="C104:I104"/>
     <mergeCell ref="C107:I107"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:I116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2560,27 +2560,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に関する4件の成果品を1件に束ねた統合報告書（新たに作った8シートと、4資料の全36シートの計44シート）。統合について、算定の全体像と採用案、月額への効きの統合一覧、記載事項の網羅点検、論点漏れと是正の方針、自己点検、確認事項、成果品の統合候補。</t>
+          <t>いま手元にある資料で算定できるところまで見込量を進めたもの（14シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、施設・居住系と必要利用定員総数、地域支援事業の量と費用、中長期推計、給付費と保険料、据え置き・既定値の一覧、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>見込量算定に関する成果品が4件に分かれていたため1件に束ねた。あわせて、介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項26件に対して論点の漏れがないかを点検し、対応5件・一部対応12件・未対応9件とした。未対応の主なものは、①中長期推計が認定者数にとどまり見込量・給付費・保険料に及んでいないこと（改正法により必須の記載事項となる）、②地域支援事業が費用の額のみで量の見込みがないこと（法第117条第2項第2号）、③令和9年4月に新設される区分を見込量に立てていないこと、④供給の制約（人材）を反映していないことである。月額への効きは24件を1表に統合し、100円超が12件・50〜100円が5件・50円未満が7件である。自己点検12件はいずれも適合している。</t>
+          <t>令和8年9月11日に年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになった。これを基礎として、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は算定上の月額基準額で＋8円である。①利用回（日）数の見込み（法第117条第2項第1号）、②地域支援事業の量の見込み（同項第2号）、③中長期推計（令和17年度・令和22年度）の見込量・給付費を新たに算定し、統合報告書が未対応としていた論点のうち3件に着手した。決着していない事項は過年度の数値を据え置き、何をどう置いたかを20件すべて掲げている。必要利用定員総数は現に指定を受けている定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。自己点検15件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>44シート</t>
+          <t>14シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>146 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2605,27 +2605,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算（9シート）。対計画比の実測、サービス別の趨勢、補正の設計とバックテスト、補正した見込量、給付費と保険料への影響、残る外れとその扱い、自己点検、確認事項。</t>
+          <t>サービス見込量の算定に関する4件の成果品を1件に束ねた統合報告書（新たに作った8シートと、4資料の全36シートの計44シート）。統合について、算定の全体像と採用案、月額への効きの統合一覧、記載事項の網羅点検、論点漏れと是正の方針、自己点検、確認事項、成果品の統合候補。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>第7期から第9期までの8年度の対計画比は、サービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満（8年平均94.93％）である。実績の伸びはサービス別に年率▲10.7％から＋28.8％まで開いており、認定者数の伸び（年率＋0.48％）とは別物である。起点と予測年数を変えた5通りのバックテストで30設定を比べ、趨勢を半分反映する置き方（φ＝0.5・上限±3％・窓5年）を選んだ。一律は30設定中15位である。補正の効きは施設・居住系を減らすかどうかで符号が変わり、月額▲58円から＋48円である。補正しても外れるサービスが6件残る。自己点検10件はいずれも適合している。</t>
+          <t>見込量算定に関する成果品が4件に分かれていたため1件に束ねた。あわせて、介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項26件に対して論点の漏れがないかを点検し、対応5件・一部対応12件・未対応9件とした。未対応の主なものは、①中長期推計が認定者数にとどまり見込量・給付費・保険料に及んでいないこと（改正法により必須の記載事項となる）、②地域支援事業が費用の額のみで量の見込みがないこと（法第117条第2項第2号）、③令和9年4月に新設される区分を見込量に立てていないこと、④供給の制約（人材）を反映していないことである。月額への効きは24件を1表に統合し、100円超が12件・50〜100円が5件・50円未満が7件である。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>44シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>146 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2643,34 +2643,34 @@
       <c r="A48" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2・表18）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り、算定の手順のチェックリスト。</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算（9シート）。対計画比の実測、サービス別の趨勢、補正の設計とバックテスト、補正した見込量、給付費と保険料への影響、残る外れとその扱い、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>本業務で確立した手順を一般化したものであり、大雪地区広域連合の計画そのものではない。同広域連合の値は適用例として明示している。方法の中心は、値を精緻にすることではなく、どの選択がどれだけ効くかを先に測り、効かないものに労力を割かないことにある。基準年度と出所を誤れば以降の精緻な作業は意味を失い、その2つが定まっていれば季節補正のような調整は誤差の範囲に収まる。</t>
+          <t>第7期から第9期までの8年度の対計画比は、サービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満（8年平均94.93％）である。実績の伸びはサービス別に年率▲10.7％から＋28.8％まで開いており、認定者数の伸び（年率＋0.48％）とは別物である。起点と予測年数を変えた5通りのバックテストで30設定を比べ、趨勢を半分反映する置き方（φ＝0.5・上限±3％・窓5年）を選んだ。一律は30設定中15位である。補正の効きは施設・居住系を減らすかどうかで符号が変わり、月額▲58円から＋48円である。補正しても外れるサービスが6件残る。自己点検10件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>197段落 18表</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2678,9 +2678,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2688,34 +2688,34 @@
       <c r="A49" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の数値が年度途中であることと、冬季と夏季の差を踏まえた補正方法の検討（9シート）。季節性の検証、令和8年度の分解、補正方法の比較と採否、施策反映の設計、施策反映の歯止め、月額への効きの一覧、自己点検、確認事項。</t>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2・表18）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り、算定の手順のチェックリスト。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>冬季と夏季の対比は、施設が＋2.80％・在宅が▲2.48％で、令和6年度・令和7年度の2年とも同じ向きに再現する。居住系と合計は測定できない。施設と在宅が逆向きであるため給付費で加重すると相殺され、年度換算係数は2.9935で一律の3.0000と0.22％しか違わない。採用パターン（令和7年度基準）は完結年度であるため季節指数の和が12となり、換算係数1.0000で季節補正は恒等的に消える。令和8年度は介護保険事業状況報告の月報により令和8年4〜7月の4か月と確定した。使いづらい主因は季節ではなく単価であり、残差は分母の採り方で＋1.63％から＋5.90％の幅がある。自己点検12件はいずれも適合している。</t>
+          <t>本業務で確立した手順を一般化したものであり、大雪地区広域連合の計画そのものではない。同広域連合の値は適用例として明示している。方法の中心は、値を精緻にすることではなく、どの選択がどれだけ効くかを先に測り、効かないものに労力を割かないことにある。基準年度と出所を誤れば以降の精緻な作業は意味を失い、その2つが定まっていれば季節補正のような調整は誤差の範囲に収まる。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>197段落 18表</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2723,9 +2723,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定について、基準年度・出所・伸ばし方の組合せごとに給付費と保険料への影響を示したもの（8シート）。基準年度の判定、出所の比較、算定パターンと妥当性、サービス見込量、給付費と保険料への影響、自己点検、確認事項。</t>
+          <t>令和8年度の数値が年度途中であることと、冬季と夏季の差を踏まえた補正方法の検討（9シート）。季節性の検証、令和8年度の分解、補正方法の比較と採否、施策反映の設計、施策反映の歯止め、月額への効きの一覧、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>数量（利用者数）の基準年度に使えるのは令和7年度だけである。令和8年度は約4か月分の実績しかなく、計画作成支援ツールの月平均利用者数は年度累計を12で除しているため令和7年度の約0.37倍の値になっている。単価（1人1月あたり給付費・利用回数）は月数に中立であり令和8年度でも使える。見える化システムの総括表は保険者単位、計画作成支援ツールは3町合計で、同じ令和7年度の利用者数でも+1.4％から+243％の開きがある。算定できた7パターンで算定上の月額基準額は6,224円から7,049円まで825円の幅がある。自己点検11件はいずれも適合している。</t>
+          <t>冬季と夏季の対比は、施設が＋2.80％・在宅が▲2.48％で、令和6年度・令和7年度の2年とも同じ向きに再現する。居住系と合計は測定できない。施設と在宅が逆向きであるため給付費で加重すると相殺され、年度換算係数は2.9935で一律の3.0000と0.22％しか違わない。採用パターン（令和7年度基準）は完結年度であるため季節指数の和が12となり、換算係数1.0000で季節補正は恒等的に消える。令和8年度は介護保険事業状況報告の月報により令和8年4〜7月の4か月と確定した。使いづらい主因は季節ではなく単価であり、残差は分母の採り方で＋1.63％から＋5.90％の幅がある。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2778,34 +2778,34 @@
       <c r="A51" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を当区域の実データと突き合わせた協議資料（10シート）。区域内の現況、論点14件の一覧と詳細、条例で定める基準の区分、令和9年4月から義務となるもの、運営推進会議の開催頻度、省令上の定員の単位、計画素案の修正、確認事項。</t>
+          <t>サービス見込量の算定について、基準年度・出所・伸ばし方の組合せごとに給付費と保険料への影響を示したもの（8シート）。基準年度の判定、出所の比較、算定パターンと妥当性、サービス見込量、給付費と保険料への影響、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>地域密着型サービスの基準は広域連合の条例で定めるものであり、省令はその条例を定めるに当たっての基準である。広域連合の指定基準条例を受領していないため、令和6年厚生労働省令第16号による改正後の省令に対応しているかを確認できていない。令和9年4月1日に義務となる協力医療機関の要件強化（10事業所）と生産性向上委員会（15事業所）も条例の対応規定を経て事業者に及ぶため、条例の確認を最も重い確認事項としている。ご指示により計画素案の本文には反映していない。ただし本作業で判明した計画素案自体の誤り3件は修正した。</t>
+          <t>数量（利用者数）の基準年度に使えるのは令和7年度だけである。令和8年度は約4か月分の実績しかなく、計画作成支援ツールの月平均利用者数は年度累計を12で除しているため令和7年度の約0.37倍の値になっている。単価（1人1月あたり給付費・利用回数）は月数に中立であり令和8年度でも使える。見える化システムの総括表は保険者単位、計画作成支援ツールは3町合計で、同じ令和7年度の利用者数でも+1.4％から+243％の開きがある。算定できた7パターンで算定上の月額基準額は6,224円から7,049円まで825円の幅がある。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>47 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料の内容を第10期計画に反映するための協議資料（9シート）。第9期計画における給付適正化の記載、国が求める記載事項との対照、第10期での位置づけ（3案）、主要3事業の毎年度の定量目標、財政調整交付金への影響、進捗管理の手引きに基づく整理、介護SCRの活用案、確認事項。</t>
+          <t>指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を当区域の実データと突き合わせた協議資料（10シート）。区域内の現況、論点14件の一覧と詳細、条例で定める基準の区分、令和9年4月から義務となるもの、運営推進会議の開催頻度、省令上の定員の単位、計画素案の修正、確認事項。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、「介護給付適正化計画」という語では記載がない。介護保険法第117条第2項第3号・第4号に対応する記載であり、第10期では第7期給付適正化計画に当たる。ご指示により計画素案の本文には反映していない。計画素案に入れるかどうかは第9期計画の体裁を勘案して協議する。</t>
+          <t>地域密着型サービスの基準は広域連合の条例で定めるものであり、省令はその条例を定めるに当たっての基準である。広域連合の指定基準条例を受領していないため、令和6年厚生労働省令第16号による改正後の省令に対応しているかを確認できていない。令和9年4月1日に義務となる協力医療機関の要件強化（10事業所）と生産性向上委員会（15事業所）も条例の対応規定を経て事業者に及ぶため、条例の確認を最も重い確認事項としている。ご指示により計画素案の本文には反映していない。ただし本作業で判明した計画素案自体の誤り3件は修正した。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
+          <t>令和8年9月10日に受領した5件の資料の内容を第10期計画に反映するための協議資料（9シート）。第9期計画における給付適正化の記載、国が求める記載事項との対照、第10期での位置づけ（3案）、主要3事業の毎年度の定量目標、財政調整交付金への影響、進捗管理の手引きに基づく整理、介護SCRの活用案、確認事項。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
+          <t>第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、「介護給付適正化計画」という語では記載がない。介護保険法第117条第2項第3号・第4号に対応する記載であり、第10期では第7期給付適正化計画に当たる。ご指示により計画素案の本文には反映していない。計画素案に入れるかどうかは第9期計画の体裁を勘案して協議する。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>119段落 17表</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2913,34 +2913,34 @@
       <c r="A54" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
+          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
+          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>119段落 17表</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2948,9 +2948,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I54" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2965,17 +2965,17 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
+          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
+          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -2993,9 +2993,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
+          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
+          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3055,27 +3055,27 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
+          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3083,9 +3083,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3100,27 +3100,27 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3145,27 +3145,27 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3190,17 +3190,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3235,17 +3235,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3273,34 +3273,34 @@
       <c r="A62" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3308,9 +3308,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3318,34 +3318,34 @@
       <c r="A63" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3353,9 +3353,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3370,17 +3370,17 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3398,9 +3398,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3408,34 +3408,34 @@
       <c r="A65" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3443,9 +3443,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3460,37 +3460,37 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I66" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3505,32 +3505,32 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I67" s="12" t="inlineStr">
@@ -3550,27 +3550,27 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>109 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3578,9 +3578,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I68" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3588,34 +3588,34 @@
       <c r="A69" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>110 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -3623,9 +3623,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3640,17 +3640,17 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
+          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -3678,34 +3678,34 @@
       <c r="A71" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>44 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -3723,34 +3723,34 @@
       <c r="A72" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>44 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3775,27 +3775,27 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -3803,9 +3803,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I73" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3820,27 +3820,27 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -3858,34 +3858,34 @@
       <c r="A75" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3893,9 +3893,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I75" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3910,27 +3910,27 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -3938,9 +3938,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3955,27 +3955,27 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -3983,9 +3983,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4000,27 +4000,27 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -4045,27 +4045,27 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -4090,17 +4090,17 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -4135,17 +4135,17 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -4180,27 +4180,27 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -4225,27 +4225,27 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -4253,9 +4253,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I83" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4270,27 +4270,27 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
@@ -4315,27 +4315,27 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -4360,17 +4360,17 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -4405,27 +4405,27 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
@@ -4433,9 +4433,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4450,27 +4450,27 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -4478,9 +4478,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4495,27 +4495,27 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -4540,27 +4540,27 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -4585,27 +4585,27 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -4623,44 +4623,44 @@
       <c r="A92" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I92" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4675,32 +4675,32 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
@@ -4720,27 +4720,27 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -4748,9 +4748,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I94" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I94" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4758,34 +4758,34 @@
       <c r="A95" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -4793,9 +4793,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4810,17 +4810,17 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -4838,9 +4838,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I96" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4848,44 +4848,44 @@
       <c r="A97" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H97" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I97" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I97" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4900,27 +4900,27 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H98" s="18" t="inlineStr">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H99" s="18" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -5035,95 +5035,119 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H101" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I101" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="52" customHeight="1">
+      <c r="A102" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D102" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E102" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G101" s="7" t="inlineStr">
+      <c r="G102" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H101" s="18" t="inlineStr">
+      <c r="H102" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I101" s="18" t="inlineStr">
+      <c r="I102" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="19" t="inlineStr">
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="28" customHeight="1">
-      <c r="A104" s="3" t="inlineStr">
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr"/>
-      <c r="E104" s="3" t="inlineStr"/>
-      <c r="F104" s="3" t="inlineStr"/>
-      <c r="G104" s="3" t="inlineStr"/>
-      <c r="H104" s="3" t="inlineStr"/>
-      <c r="I104" s="3" t="inlineStr"/>
-    </row>
-    <row r="105" ht="32" customHeight="1">
-      <c r="A105" s="5" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr"/>
+      <c r="E105" s="3" t="inlineStr"/>
+      <c r="F105" s="3" t="inlineStr"/>
+      <c r="G105" s="3" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106" ht="32" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D105" s="20" t="n"/>
-      <c r="E105" s="20" t="n"/>
-      <c r="F105" s="20" t="n"/>
-      <c r="G105" s="20" t="n"/>
-      <c r="H105" s="20" t="n"/>
-      <c r="I105" s="21" t="n"/>
-    </row>
-    <row r="106" ht="32" customHeight="1">
-      <c r="A106" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B106" s="6" t="n">
@@ -5131,7 +5155,7 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D106" s="20" t="n"/>
@@ -5142,17 +5166,17 @@
       <c r="I106" s="21" t="n"/>
     </row>
     <row r="107" ht="32" customHeight="1">
-      <c r="A107" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A107" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D107" s="20" t="n"/>
@@ -5163,17 +5187,17 @@
       <c r="I107" s="21" t="n"/>
     </row>
     <row r="108" ht="32" customHeight="1">
-      <c r="A108" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A108" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B108" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D108" s="20" t="n"/>
@@ -5184,17 +5208,17 @@
       <c r="I108" s="21" t="n"/>
     </row>
     <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A109" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D109" s="20" t="n"/>
@@ -5205,17 +5229,17 @@
       <c r="I109" s="21" t="n"/>
     </row>
     <row r="110" ht="32" customHeight="1">
-      <c r="A110" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B110" s="6" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、サービス見込量の算定_第1次概算、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D110" s="20" t="n"/>
@@ -5226,17 +5250,17 @@
       <c r="I110" s="21" t="n"/>
     </row>
     <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A111" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D111" s="20" t="n"/>
@@ -5247,17 +5271,17 @@
       <c r="I111" s="21" t="n"/>
     </row>
     <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B112" s="6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D112" s="20" t="n"/>
@@ -5267,18 +5291,18 @@
       <c r="H112" s="20" t="n"/>
       <c r="I112" s="21" t="n"/>
     </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B113" s="22" t="n">
-        <v>97</v>
-      </c>
-      <c r="C113" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの92件、別スコープ5件</t>
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D113" s="20" t="n"/>
@@ -5288,8 +5312,29 @@
       <c r="H113" s="20" t="n"/>
       <c r="I113" s="21" t="n"/>
     </row>
-    <row r="115" ht="100" customHeight="1">
-      <c r="A115" s="23" t="inlineStr">
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B114" s="22" t="n">
+        <v>98</v>
+      </c>
+      <c r="C114" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの93件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D114" s="20" t="n"/>
+      <c r="E114" s="20" t="n"/>
+      <c r="F114" s="20" t="n"/>
+      <c r="G114" s="20" t="n"/>
+      <c r="H114" s="20" t="n"/>
+      <c r="I114" s="21" t="n"/>
+    </row>
+    <row r="116" ht="100" customHeight="1">
+      <c r="A116" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -5297,15 +5342,15 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A104:I104"/>
     <mergeCell ref="C111:I111"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C110:I110"/>
-    <mergeCell ref="A103:I103"/>
+    <mergeCell ref="C114:I114"/>
     <mergeCell ref="C106:I106"/>
-    <mergeCell ref="C105:I105"/>
     <mergeCell ref="C113:I113"/>
-    <mergeCell ref="A115:H115"/>
     <mergeCell ref="C109:I109"/>
+    <mergeCell ref="A116:H116"/>
     <mergeCell ref="C112:I112"/>
     <mergeCell ref="C108:I108"/>
     <mergeCell ref="C107:I107"/>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3550,27 +3550,27 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検（8シート）。算定式の対照、保険料の式の突合、受給率の分母の粒度による差の実測、見える化システムの画面との不一致、入力の落とし穴、作成者へ返せる情報。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>算定式の骨格は当方と同じであり、差は受給率の分母の粒度だけである。要介護度7区分（当方）と要介護・要支援の2区分（アプリ）の差は第10期3か年で月額3円、令和22年度で0.22％である。アプリの保険料の式（収納見込＝月額×補正後被保険者延人数×収納率）に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢4件はいずれも令和8年度が終期側に来るもので、令和6年度→令和7年度のみが令和8年度を含まない。作業過程の記録であり、送付資料としては用いない（内部保管）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>110 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -3623,9 +3623,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I69" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3633,34 +3633,34 @@
       <c r="A70" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>110 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -3668,9 +3668,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I70" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3685,17 +3685,17 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
+          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -3723,34 +3723,34 @@
       <c r="A72" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>44 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3768,34 +3768,34 @@
       <c r="A73" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>44 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -3820,27 +3820,27 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -3848,9 +3848,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I74" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3865,27 +3865,27 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3903,34 +3903,34 @@
       <c r="A76" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -3938,9 +3938,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I76" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3955,27 +3955,27 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -3983,9 +3983,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4000,27 +4000,27 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -4028,9 +4028,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4045,27 +4045,27 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -4090,27 +4090,27 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -4135,17 +4135,17 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -4180,17 +4180,17 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -4225,27 +4225,27 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -4270,27 +4270,27 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
@@ -4298,9 +4298,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I84" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4315,27 +4315,27 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -4360,27 +4360,27 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -4405,17 +4405,17 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -4450,27 +4450,27 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -4478,9 +4478,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4495,27 +4495,27 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -4523,9 +4523,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4540,27 +4540,27 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -4585,27 +4585,27 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -4630,27 +4630,27 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -4668,44 +4668,44 @@
       <c r="A93" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I93" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4720,32 +4720,32 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I94" s="12" t="inlineStr">
@@ -4765,27 +4765,27 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -4793,9 +4793,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I95" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4803,34 +4803,34 @@
       <c r="A96" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -4838,9 +4838,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4855,17 +4855,17 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
@@ -4883,9 +4883,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I97" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4893,44 +4893,44 @@
       <c r="A98" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H98" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I98" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I98" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4945,27 +4945,27 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H99" s="18" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H100" s="18" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -5080,95 +5080,119 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H102" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I102" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="52" customHeight="1">
+      <c r="A103" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B103" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="D103" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G102" s="7" t="inlineStr">
+      <c r="G103" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H102" s="18" t="inlineStr">
+      <c r="H103" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I102" s="18" t="inlineStr">
+      <c r="I103" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="19" t="inlineStr">
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="28" customHeight="1">
-      <c r="A105" s="3" t="inlineStr">
+    <row r="106" ht="28" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr"/>
-      <c r="E105" s="3" t="inlineStr"/>
-      <c r="F105" s="3" t="inlineStr"/>
-      <c r="G105" s="3" t="inlineStr"/>
-      <c r="H105" s="3" t="inlineStr"/>
-      <c r="I105" s="3" t="inlineStr"/>
-    </row>
-    <row r="106" ht="32" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr"/>
+      <c r="E106" s="3" t="inlineStr"/>
+      <c r="F106" s="3" t="inlineStr"/>
+      <c r="G106" s="3" t="inlineStr"/>
+      <c r="H106" s="3" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107" ht="32" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D106" s="20" t="n"/>
-      <c r="E106" s="20" t="n"/>
-      <c r="F106" s="20" t="n"/>
-      <c r="G106" s="20" t="n"/>
-      <c r="H106" s="20" t="n"/>
-      <c r="I106" s="21" t="n"/>
-    </row>
-    <row r="107" ht="32" customHeight="1">
-      <c r="A107" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
@@ -5176,7 +5200,7 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D107" s="20" t="n"/>
@@ -5187,17 +5211,17 @@
       <c r="I107" s="21" t="n"/>
     </row>
     <row r="108" ht="32" customHeight="1">
-      <c r="A108" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A108" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B108" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D108" s="20" t="n"/>
@@ -5208,17 +5232,17 @@
       <c r="I108" s="21" t="n"/>
     </row>
     <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A109" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、入力前段支援アプリの点検、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D109" s="20" t="n"/>
@@ -5229,17 +5253,17 @@
       <c r="I109" s="21" t="n"/>
     </row>
     <row r="110" ht="32" customHeight="1">
-      <c r="A110" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A110" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B110" s="6" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、サービス見込量の算定_第1次概算、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D110" s="20" t="n"/>
@@ -5250,17 +5274,17 @@
       <c r="I110" s="21" t="n"/>
     </row>
     <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、サービス見込量の算定_第1次概算、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D111" s="20" t="n"/>
@@ -5271,17 +5295,17 @@
       <c r="I111" s="21" t="n"/>
     </row>
     <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A112" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B112" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D112" s="20" t="n"/>
@@ -5292,17 +5316,17 @@
       <c r="I112" s="21" t="n"/>
     </row>
     <row r="113" ht="32" customHeight="1">
-      <c r="A113" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D113" s="20" t="n"/>
@@ -5312,18 +5336,18 @@
       <c r="H113" s="20" t="n"/>
       <c r="I113" s="21" t="n"/>
     </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B114" s="22" t="n">
-        <v>98</v>
-      </c>
-      <c r="C114" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの93件、別スコープ5件</t>
+    <row r="114" ht="32" customHeight="1">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D114" s="20" t="n"/>
@@ -5333,8 +5357,29 @@
       <c r="H114" s="20" t="n"/>
       <c r="I114" s="21" t="n"/>
     </row>
-    <row r="116" ht="100" customHeight="1">
-      <c r="A116" s="23" t="inlineStr">
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B115" s="22" t="n">
+        <v>99</v>
+      </c>
+      <c r="C115" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの94件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D115" s="20" t="n"/>
+      <c r="E115" s="20" t="n"/>
+      <c r="F115" s="20" t="n"/>
+      <c r="G115" s="20" t="n"/>
+      <c r="H115" s="20" t="n"/>
+      <c r="I115" s="21" t="n"/>
+    </row>
+    <row r="117" ht="100" customHeight="1">
+      <c r="A117" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -5342,17 +5387,17 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A104:I104"/>
     <mergeCell ref="C111:I111"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C110:I110"/>
     <mergeCell ref="C114:I114"/>
-    <mergeCell ref="C106:I106"/>
+    <mergeCell ref="A117:H117"/>
     <mergeCell ref="C113:I113"/>
     <mergeCell ref="C109:I109"/>
-    <mergeCell ref="A116:H116"/>
+    <mergeCell ref="C115:I115"/>
+    <mergeCell ref="A105:I105"/>
+    <mergeCell ref="C108:I108"/>
     <mergeCell ref="C112:I112"/>
-    <mergeCell ref="C108:I108"/>
     <mergeCell ref="C107:I107"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -2565,22 +2565,22 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>いま手元にある資料で算定できるところまで見込量を進めたもの（14シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、施設・居住系と必要利用定員総数、地域支援事業の量と費用、中長期推計、給付費と保険料、据え置き・既定値の一覧、自己点検、確認事項。</t>
+          <t>いま手元にある資料で算定できるところまで見込量を進めたもの（18シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、要介護度別の給付費、在宅と施設の連鎖、施設・居住系と必要利用定員総数、供給の制約（定員上限）と在宅への振替、地域支援事業の量と費用、中長期推計、給付費と保険料、報酬改定率の感度、据え置き・既定値の一覧、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになった。これを基礎として、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は算定上の月額基準額で＋8円である。①利用回（日）数の見込み（法第117条第2項第1号）、②地域支援事業の量の見込み（同項第2号）、③中長期推計（令和17年度・令和22年度）の見込量・給付費を新たに算定し、統合報告書が未対応としていた論点のうち3件に着手した。決着していない事項は過年度の数値を据え置き、何をどう置いたかを20件すべて掲げている。必要利用定員総数は現に指定を受けている定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。自己点検15件はいずれも適合している。</t>
+          <t>令和8年9月11日に年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになった。これを基礎として、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は算定上の月額基準額で＋8円である。①利用回（日）数の見込み（法第117条第2項第1号）、②地域支援事業の量の見込み（同項第2号）、③中長期推計（令和17年度・令和22年度）の見込量・給付費、④要介護度別の給付費、⑤供給の制約（定員上限）と在宅への振替、⑥報酬改定率の感度を新たに算定し、統合報告書が未対応としていた論点のうち4件に着手した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に区域内の定員の99.9％に達し、令和17年度には超える。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現に指定を受けている定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。自己点検22件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>14シート</t>
+          <t>18シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>73 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>26 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>110 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（843段落137表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（886段落142表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>843段落 137表</t>
+          <t>886段落 142表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>36 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>44 KB</t>
+          <t>45 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（843段落137表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（886段落142表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（886段落142表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（893段落143表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>886段落 142表</t>
+          <t>893段落 143表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>112 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（886段落142表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（893段落143表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I117"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2560,27 +2560,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>いま手元にある資料で算定できるところまで見込量を進めたもの（18シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、要介護度別の給付費、在宅と施設の連鎖、施設・居住系と必要利用定員総数、供給の制約（定員上限）と在宅への振替、地域支援事業の量と費用、中長期推計、給付費と保険料、報酬改定率の感度、据え置き・既定値の一覧、自己点検、確認事項。</t>
+          <t>共生社会の実現を推進するための認知症基本法第13条の市町村認知症施策推進計画をどう扱うかの検討資料（10シート）。法の規定と当広域連合の関係、計画素案の現状、位置づけの3案、認知症に関する数量、交付金評価の町別、見込量算定への反映、意見聴取の設計、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになった。これを基礎として、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は算定上の月額基準額で＋8円である。①利用回（日）数の見込み（法第117条第2項第1号）、②地域支援事業の量の見込み（同項第2号）、③中長期推計（令和17年度・令和22年度）の見込量・給付費、④要介護度別の給付費、⑤供給の制約（定員上限）と在宅への振替、⑥報酬改定率の感度を新たに算定し、統合報告書が未対応としていた論点のうち4件に着手した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に区域内の定員の99.9％に達し、令和17年度には超える。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現に指定を受けている定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。自己点検22件はいずれも適合している。</t>
+          <t>諮る資料であり計画素案には入れていない。同法の名宛人は「市町村」であり、広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体であるから、広域連合の計画に一体のものとして定めても市町村計画としての効力は生じない。構成3町がそれぞれ策定し、広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案を推す。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込み（前年比▲14.7％）は1事業所の定員縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>18シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>73 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2605,27 +2605,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に関する4件の成果品を1件に束ねた統合報告書（新たに作った8シートと、4資料の全36シートの計44シート）。統合について、算定の全体像と採用案、月額への効きの統合一覧、記載事項の網羅点検、論点漏れと是正の方針、自己点検、確認事項、成果品の統合候補。</t>
+          <t>いま手元にある資料で算定できるところまで見込量を進めたもの（18シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、要介護度別の給付費、在宅と施設の連鎖、施設・居住系と必要利用定員総数、供給の制約（定員上限）と在宅への振替、地域支援事業の量と費用、中長期推計、給付費と保険料、報酬改定率の感度、据え置き・既定値の一覧、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>見込量算定に関する成果品が4件に分かれていたため1件に束ねた。あわせて、介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項26件に対して論点の漏れがないかを点検し、対応5件・一部対応12件・未対応9件とした。未対応の主なものは、①中長期推計が認定者数にとどまり見込量・給付費・保険料に及んでいないこと（改正法により必須の記載事項となる）、②地域支援事業が費用の額のみで量の見込みがないこと（法第117条第2項第2号）、③令和9年4月に新設される区分を見込量に立てていないこと、④供給の制約（人材）を反映していないことである。月額への効きは24件を1表に統合し、100円超が12件・50〜100円が5件・50円未満が7件である。自己点検12件はいずれも適合している。</t>
+          <t>令和8年9月11日に年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになった。これを基礎として、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は算定上の月額基準額で＋8円である。①利用回（日）数の見込み（法第117条第2項第1号）、②地域支援事業の量の見込み（同項第2号）、③中長期推計（令和17年度・令和22年度）の見込量・給付費、④要介護度別の給付費、⑤供給の制約（定員上限）と在宅への振替、⑥報酬改定率の感度を新たに算定し、統合報告書が未対応としていた論点のうち4件に着手した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に区域内の定員の99.9％に達し、令和17年度には超える。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現に指定を受けている定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。自己点検22件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>44シート</t>
+          <t>18シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>146 KB</t>
+          <t>73 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2650,27 +2650,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算（9シート）。対計画比の実測、サービス別の趨勢、補正の設計とバックテスト、補正した見込量、給付費と保険料への影響、残る外れとその扱い、自己点検、確認事項。</t>
+          <t>サービス見込量の算定に関する4件の成果品を1件に束ねた統合報告書（新たに作った8シートと、4資料の全36シートの計44シート）。統合について、算定の全体像と採用案、月額への効きの統合一覧、記載事項の網羅点検、論点漏れと是正の方針、自己点検、確認事項、成果品の統合候補。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>第7期から第9期までの8年度の対計画比は、サービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満（8年平均94.93％）である。実績の伸びはサービス別に年率▲10.7％から＋28.8％まで開いており、認定者数の伸び（年率＋0.48％）とは別物である。起点と予測年数を変えた5通りのバックテストで30設定を比べ、趨勢を半分反映する置き方（φ＝0.5・上限±3％・窓5年）を選んだ。一律は30設定中15位である。補正の効きは施設・居住系を減らすかどうかで符号が変わり、月額▲58円から＋48円である。補正しても外れるサービスが6件残る。自己点検10件はいずれも適合している。</t>
+          <t>見込量算定に関する成果品が4件に分かれていたため1件に束ねた。あわせて、介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項26件に対して論点の漏れがないかを点検し、対応5件・一部対応12件・未対応9件とした。未対応の主なものは、①中長期推計が認定者数にとどまり見込量・給付費・保険料に及んでいないこと（改正法により必須の記載事項となる）、②地域支援事業が費用の額のみで量の見込みがないこと（法第117条第2項第2号）、③令和9年4月に新設される区分を見込量に立てていないこと、④供給の制約（人材）を反映していないことである。月額への効きは24件を1表に統合し、100円超が12件・50〜100円が5件・50円未満が7件である。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>44シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>146 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2688,34 +2688,34 @@
       <c r="A49" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2・表18）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り、算定の手順のチェックリスト。</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算（9シート）。対計画比の実測、サービス別の趨勢、補正の設計とバックテスト、補正した見込量、給付費と保険料への影響、残る外れとその扱い、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>本業務で確立した手順を一般化したものであり、大雪地区広域連合の計画そのものではない。同広域連合の値は適用例として明示している。方法の中心は、値を精緻にすることではなく、どの選択がどれだけ効くかを先に測り、効かないものに労力を割かないことにある。基準年度と出所を誤れば以降の精緻な作業は意味を失い、その2つが定まっていれば季節補正のような調整は誤差の範囲に収まる。</t>
+          <t>第7期から第9期までの8年度の対計画比は、サービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満（8年平均94.93％）である。実績の伸びはサービス別に年率▲10.7％から＋28.8％まで開いており、認定者数の伸び（年率＋0.48％）とは別物である。起点と予測年数を変えた5通りのバックテストで30設定を比べ、趨勢を半分反映する置き方（φ＝0.5・上限±3％・窓5年）を選んだ。一律は30設定中15位である。補正の効きは施設・居住系を減らすかどうかで符号が変わり、月額▲58円から＋48円である。補正しても外れるサービスが6件残る。自己点検10件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>197段落 18表</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2723,9 +2723,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2733,34 +2733,34 @@
       <c r="A50" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の数値が年度途中であることと、冬季と夏季の差を踏まえた補正方法の検討（9シート）。季節性の検証、令和8年度の分解、補正方法の比較と採否、施策反映の設計、施策反映の歯止め、月額への効きの一覧、自己点検、確認事項。</t>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2・表18）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り、算定の手順のチェックリスト。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>冬季と夏季の対比は、施設が＋2.80％・在宅が▲2.48％で、令和6年度・令和7年度の2年とも同じ向きに再現する。居住系と合計は測定できない。施設と在宅が逆向きであるため給付費で加重すると相殺され、年度換算係数は2.9935で一律の3.0000と0.22％しか違わない。採用パターン（令和7年度基準）は完結年度であるため季節指数の和が12となり、換算係数1.0000で季節補正は恒等的に消える。令和8年度は介護保険事業状況報告の月報により令和8年4〜7月の4か月と確定した。使いづらい主因は季節ではなく単価であり、残差は分母の採り方で＋1.63％から＋5.90％の幅がある。自己点検12件はいずれも適合している。</t>
+          <t>本業務で確立した手順を一般化したものであり、大雪地区広域連合の計画そのものではない。同広域連合の値は適用例として明示している。方法の中心は、値を精緻にすることではなく、どの選択がどれだけ効くかを先に測り、効かないものに労力を割かないことにある。基準年度と出所を誤れば以降の精緻な作業は意味を失い、その2つが定まっていれば季節補正のような調整は誤差の範囲に収まる。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>197段落 18表</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2768,9 +2768,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2785,27 +2785,27 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定について、基準年度・出所・伸ばし方の組合せごとに給付費と保険料への影響を示したもの（8シート）。基準年度の判定、出所の比較、算定パターンと妥当性、サービス見込量、給付費と保険料への影響、自己点検、確認事項。</t>
+          <t>令和8年度の数値が年度途中であることと、冬季と夏季の差を踏まえた補正方法の検討（9シート）。季節性の検証、令和8年度の分解、補正方法の比較と採否、施策反映の設計、施策反映の歯止め、月額への効きの一覧、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>数量（利用者数）の基準年度に使えるのは令和7年度だけである。令和8年度は約4か月分の実績しかなく、計画作成支援ツールの月平均利用者数は年度累計を12で除しているため令和7年度の約0.37倍の値になっている。単価（1人1月あたり給付費・利用回数）は月数に中立であり令和8年度でも使える。見える化システムの総括表は保険者単位、計画作成支援ツールは3町合計で、同じ令和7年度の利用者数でも+1.4％から+243％の開きがある。算定できた7パターンで算定上の月額基準額は6,224円から7,049円まで825円の幅がある。自己点検11件はいずれも適合している。</t>
+          <t>冬季と夏季の対比は、施設が＋2.80％・在宅が▲2.48％で、令和6年度・令和7年度の2年とも同じ向きに再現する。居住系と合計は測定できない。施設と在宅が逆向きであるため給付費で加重すると相殺され、年度換算係数は2.9935で一律の3.0000と0.22％しか違わない。採用パターン（令和7年度基準）は完結年度であるため季節指数の和が12となり、換算係数1.0000で季節補正は恒等的に消える。令和8年度は介護保険事業状況報告の月報により令和8年4〜7月の4か月と確定した。使いづらい主因は季節ではなく単価であり、残差は分母の採り方で＋1.63％から＋5.90％の幅がある。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2823,34 +2823,34 @@
       <c r="A52" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を当区域の実データと突き合わせた協議資料（10シート）。区域内の現況、論点14件の一覧と詳細、条例で定める基準の区分、令和9年4月から義務となるもの、運営推進会議の開催頻度、省令上の定員の単位、計画素案の修正、確認事項。</t>
+          <t>サービス見込量の算定について、基準年度・出所・伸ばし方の組合せごとに給付費と保険料への影響を示したもの（8シート）。基準年度の判定、出所の比較、算定パターンと妥当性、サービス見込量、給付費と保険料への影響、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>地域密着型サービスの基準は広域連合の条例で定めるものであり、省令はその条例を定めるに当たっての基準である。広域連合の指定基準条例を受領していないため、令和6年厚生労働省令第16号による改正後の省令に対応しているかを確認できていない。令和9年4月1日に義務となる協力医療機関の要件強化（10事業所）と生産性向上委員会（15事業所）も条例の対応規定を経て事業者に及ぶため、条例の確認を最も重い確認事項としている。ご指示により計画素案の本文には反映していない。ただし本作業で判明した計画素案自体の誤り3件は修正した。</t>
+          <t>数量（利用者数）の基準年度に使えるのは令和7年度だけである。令和8年度は約4か月分の実績しかなく、計画作成支援ツールの月平均利用者数は年度累計を12で除しているため令和7年度の約0.37倍の値になっている。単価（1人1月あたり給付費・利用回数）は月数に中立であり令和8年度でも使える。見える化システムの総括表は保険者単位、計画作成支援ツールは3町合計で、同じ令和7年度の利用者数でも+1.4％から+243％の開きがある。算定できた7パターンで算定上の月額基準額は6,224円から7,049円まで825円の幅がある。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>47 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料の内容を第10期計画に反映するための協議資料（9シート）。第9期計画における給付適正化の記載、国が求める記載事項との対照、第10期での位置づけ（3案）、主要3事業の毎年度の定量目標、財政調整交付金への影響、進捗管理の手引きに基づく整理、介護SCRの活用案、確認事項。</t>
+          <t>指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を当区域の実データと突き合わせた協議資料（10シート）。区域内の現況、論点14件の一覧と詳細、条例で定める基準の区分、令和9年4月から義務となるもの、運営推進会議の開催頻度、省令上の定員の単位、計画素案の修正、確認事項。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、「介護給付適正化計画」という語では記載がない。介護保険法第117条第2項第3号・第4号に対応する記載であり、第10期では第7期給付適正化計画に当たる。ご指示により計画素案の本文には反映していない。計画素案に入れるかどうかは第9期計画の体裁を勘案して協議する。</t>
+          <t>地域密着型サービスの基準は広域連合の条例で定めるものであり、省令はその条例を定めるに当たっての基準である。広域連合の指定基準条例を受領していないため、令和6年厚生労働省令第16号による改正後の省令に対応しているかを確認できていない。令和9年4月1日に義務となる協力医療機関の要件強化（10事業所）と生産性向上委員会（15事業所）も条例の対応規定を経て事業者に及ぶため、条例の確認を最も重い確認事項としている。ご指示により計画素案の本文には反映していない。ただし本作業で判明した計画素案自体の誤り3件は修正した。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2920,27 +2920,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
+          <t>令和8年9月10日に受領した5件の資料の内容を第10期計画に反映するための協議資料（9シート）。第9期計画における給付適正化の記載、国が求める記載事項との対照、第10期での位置づけ（3案）、主要3事業の毎年度の定量目標、財政調整交付金への影響、進捗管理の手引きに基づく整理、介護SCRの活用案、確認事項。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
+          <t>第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、「介護給付適正化計画」という語では記載がない。介護保険法第117条第2項第3号・第4号に対応する記載であり、第10期では第7期給付適正化計画に当たる。ご指示により計画素案の本文には反映していない。計画素案に入れるかどうかは第9期計画の体裁を勘案して協議する。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>119段落 17表</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2958,34 +2958,34 @@
       <c r="A55" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
+          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
+          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>119段落 17表</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -2993,9 +2993,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3010,17 +3010,17 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
+          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
+          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3038,9 +3038,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3055,27 +3055,27 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
+          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
+          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3100,27 +3100,27 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
+          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3128,9 +3128,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3145,27 +3145,27 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3190,27 +3190,27 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3235,17 +3235,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3280,17 +3280,17 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3318,34 +3318,34 @@
       <c r="A63" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3353,9 +3353,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3363,34 +3363,34 @@
       <c r="A64" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3398,9 +3398,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3415,17 +3415,17 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3443,9 +3443,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3453,34 +3453,34 @@
       <c r="A66" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>26 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3488,9 +3488,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I66" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3505,37 +3505,37 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>26 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I67" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3550,32 +3550,32 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検（8シート）。算定式の対照、保険料の式の突合、受給率の分母の粒度による差の実測、見える化システムの画面との不一致、入力の落とし穴、作成者へ返せる情報。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>算定式の骨格は当方と同じであり、差は受給率の分母の粒度だけである。要介護度7区分（当方）と要介護・要支援の2区分（アプリ）の差は第10期3か年で月額3円、令和22年度で0.22％である。アプリの保険料の式（収納見込＝月額×補正後被保険者延人数×収納率）に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢4件はいずれも令和8年度が終期側に来るもので、令和6年度→令和7年度のみが令和8年度を含まない。作業過程の記録であり、送付資料としては用いない（内部保管）。自己点検11件はいずれも適合している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I68" s="12" t="inlineStr">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検（8シート）。算定式の対照、保険料の式の突合、受給率の分母の粒度による差の実測、見える化システムの画面との不一致、入力の落とし穴、作成者へ返せる情報。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>算定式の骨格は当方と同じであり、差は受給率の分母の粒度だけである。要介護度7区分（当方）と要介護・要支援の2区分（アプリ）の差は第10期3か年で月額3円、令和22年度で0.22％である。アプリの保険料の式（収納見込＝月額×補正後被保険者延人数×収納率）に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢4件はいずれも令和8年度が終期側に来るもので、令和6年度→令和7年度のみが令和8年度を含まない。作業過程の記録であり、送付資料としては用いない（内部保管）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -3640,27 +3640,27 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>112 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -3668,9 +3668,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I70" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3678,34 +3678,34 @@
       <c r="A71" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>113 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -3713,9 +3713,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3730,17 +3730,17 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
+          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>36 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3768,34 +3768,34 @@
       <c r="A73" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>45 KB</t>
+          <t>36 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -3813,34 +3813,34 @@
       <c r="A74" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>45 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -3865,27 +3865,27 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3893,9 +3893,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I75" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3910,27 +3910,27 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -3948,34 +3948,34 @@
       <c r="A77" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -3983,9 +3983,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I77" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4000,27 +4000,27 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -4028,9 +4028,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I78" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4045,27 +4045,27 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -4073,9 +4073,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4090,27 +4090,27 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -4135,27 +4135,27 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -4180,17 +4180,17 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -4225,17 +4225,17 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -4270,27 +4270,27 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
@@ -4315,27 +4315,27 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -4343,9 +4343,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I85" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4360,27 +4360,27 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -4405,27 +4405,27 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
@@ -4450,17 +4450,17 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -4495,27 +4495,27 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -4523,9 +4523,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I89" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4540,27 +4540,27 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -4568,9 +4568,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I90" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4585,27 +4585,27 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -4630,27 +4630,27 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -4675,27 +4675,27 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
@@ -4713,44 +4713,44 @@
       <c r="A94" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I94" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4765,32 +4765,32 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
@@ -4810,27 +4810,27 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -4838,9 +4838,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I96" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I96" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4848,34 +4848,34 @@
       <c r="A97" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
@@ -4883,9 +4883,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4900,17 +4900,17 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -4928,9 +4928,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I98" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4938,44 +4938,44 @@
       <c r="A99" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H99" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I99" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I99" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4990,27 +4990,27 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H100" s="18" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H101" s="18" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -5125,95 +5125,119 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H103" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I103" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="52" customHeight="1">
+      <c r="A104" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="D104" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E104" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G103" s="7" t="inlineStr">
+      <c r="G104" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H103" s="18" t="inlineStr">
+      <c r="H104" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I103" s="18" t="inlineStr">
+      <c r="I104" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="19" t="inlineStr">
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="28" customHeight="1">
-      <c r="A106" s="3" t="inlineStr">
+    <row r="107" ht="28" customHeight="1">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr"/>
-      <c r="E106" s="3" t="inlineStr"/>
-      <c r="F106" s="3" t="inlineStr"/>
-      <c r="G106" s="3" t="inlineStr"/>
-      <c r="H106" s="3" t="inlineStr"/>
-      <c r="I106" s="3" t="inlineStr"/>
-    </row>
-    <row r="107" ht="32" customHeight="1">
-      <c r="A107" s="5" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr"/>
+      <c r="E107" s="3" t="inlineStr"/>
+      <c r="F107" s="3" t="inlineStr"/>
+      <c r="G107" s="3" t="inlineStr"/>
+      <c r="H107" s="3" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108" ht="32" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D107" s="20" t="n"/>
-      <c r="E107" s="20" t="n"/>
-      <c r="F107" s="20" t="n"/>
-      <c r="G107" s="20" t="n"/>
-      <c r="H107" s="20" t="n"/>
-      <c r="I107" s="21" t="n"/>
-    </row>
-    <row r="108" ht="32" customHeight="1">
-      <c r="A108" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B108" s="6" t="n">
@@ -5221,7 +5245,7 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D108" s="20" t="n"/>
@@ -5232,17 +5256,17 @@
       <c r="I108" s="21" t="n"/>
     </row>
     <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A109" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、入力前段支援アプリの点検、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D109" s="20" t="n"/>
@@ -5253,17 +5277,17 @@
       <c r="I109" s="21" t="n"/>
     </row>
     <row r="110" ht="32" customHeight="1">
-      <c r="A110" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A110" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B110" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、入力前段支援アプリの点検、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D110" s="20" t="n"/>
@@ -5274,17 +5298,17 @@
       <c r="I110" s="21" t="n"/>
     </row>
     <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A111" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、サービス見込量の算定_第1次概算、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D111" s="20" t="n"/>
@@ -5295,17 +5319,17 @@
       <c r="I111" s="21" t="n"/>
     </row>
     <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B112" s="6" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、認知症施策推進計画の位置づけと見込量への反映、サービス見込量の算定_第1次概算、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D112" s="20" t="n"/>
@@ -5316,17 +5340,17 @@
       <c r="I112" s="21" t="n"/>
     </row>
     <row r="113" ht="32" customHeight="1">
-      <c r="A113" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A113" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D113" s="20" t="n"/>
@@ -5337,17 +5361,17 @@
       <c r="I113" s="21" t="n"/>
     </row>
     <row r="114" ht="32" customHeight="1">
-      <c r="A114" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B114" s="6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D114" s="20" t="n"/>
@@ -5357,18 +5381,18 @@
       <c r="H114" s="20" t="n"/>
       <c r="I114" s="21" t="n"/>
     </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B115" s="22" t="n">
-        <v>99</v>
-      </c>
-      <c r="C115" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの94件、別スコープ5件</t>
+    <row r="115" ht="32" customHeight="1">
+      <c r="A115" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D115" s="20" t="n"/>
@@ -5378,8 +5402,29 @@
       <c r="H115" s="20" t="n"/>
       <c r="I115" s="21" t="n"/>
     </row>
-    <row r="117" ht="100" customHeight="1">
-      <c r="A117" s="23" t="inlineStr">
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B116" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C116" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの95件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D116" s="20" t="n"/>
+      <c r="E116" s="20" t="n"/>
+      <c r="F116" s="20" t="n"/>
+      <c r="G116" s="20" t="n"/>
+      <c r="H116" s="20" t="n"/>
+      <c r="I116" s="21" t="n"/>
+    </row>
+    <row r="118" ht="100" customHeight="1">
+      <c r="A118" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -5391,14 +5436,14 @@
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C110:I110"/>
     <mergeCell ref="C114:I114"/>
-    <mergeCell ref="A117:H117"/>
     <mergeCell ref="C113:I113"/>
     <mergeCell ref="C109:I109"/>
+    <mergeCell ref="A106:I106"/>
+    <mergeCell ref="A118:H118"/>
     <mergeCell ref="C115:I115"/>
-    <mergeCell ref="A105:I105"/>
+    <mergeCell ref="C112:I112"/>
     <mergeCell ref="C108:I108"/>
-    <mergeCell ref="C112:I112"/>
-    <mergeCell ref="C107:I107"/>
+    <mergeCell ref="C116:I116"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（893段落143表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（896段落143表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>893段落 143表</t>
+          <t>896段落 143表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>諮る資料であり計画素案には入れていない。同法の名宛人は「市町村」であり、広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体であるから、広域連合の計画に一体のものとして定めても市町村計画としての効力は生じない。構成3町がそれぞれ策定し、広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案を推す。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込み（前年比▲14.7％）は1事業所の定員縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。自己点検11件はいずれも適合している。</t>
+          <t>令和8年9月16日に案Bを採用し、計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映した（新たな節・章は起こしていない）。同法の名宛人は「市町村」であり、広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体であるから、広域連合の計画に一体のものとして定めても市町村計画としての効力は生じない。構成3町がそれぞれ策定し、広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案である。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込み（前年比▲14.7％）は1事業所の定員縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（893段落143表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（896段落143表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>113 KB</t>
+          <t>114 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>114 KB</t>
+          <t>119 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>482段落 52表</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>65 KB</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2650,27 +2650,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に関する4件の成果品を1件に束ねた統合報告書（新たに作った8シートと、4資料の全36シートの計44シート）。統合について、算定の全体像と採用案、月額への効きの統合一覧、記載事項の網羅点検、論点漏れと是正の方針、自己点検、確認事項、成果品の統合候補。</t>
+          <t>追加の資料が届かない前提でのサービス見込量（全11節・表17点）。サービス見込量29区分、利用回（日）数12区分、地域支援事業の量12項目、給付費、保険料算定表の記号A〜J、必要利用定員総数、中長期推計、据え置き23件の区分、月額基準額の幅、計画本文への注記の案。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>見込量算定に関する成果品が4件に分かれていたため1件に束ねた。あわせて、介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項26件に対して論点の漏れがないかを点検し、対応5件・一部対応12件・未対応9件とした。未対応の主なものは、①中長期推計が認定者数にとどまり見込量・給付費・保険料に及んでいないこと（改正法により必須の記載事項となる）、②地域支援事業が費用の額のみで量の見込みがないこと（法第117条第2項第2号）、③令和9年4月に新設される区分を見込量に立てていないこと、④供給の制約（人材）を反映していないことである。月額への効きは24件を1表に統合し、100円超が12件・50〜100円が5件・50円未満が7件である。自己点検12件はいずれも適合している。</t>
+          <t>サービス見込量の算定 第1次概算（令和8年9月16日）が、そのまま「資料が届かない前提」の見込量であることを示したもの。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円で、百円未満四捨五入した保険料基準額は6,400円となり第9期と同額である。据え置き23件を出どころで分けると、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件である。発注者・3町から追加の資料がまったく届かなくても、国の告示さえ出れば計画は確定する。ただし6,436円は据え置き前提の下限に近く、単価の趨勢（＋185〜＋374円）や報酬改定率（3％で＋182円）、第1号被保険者負担割合の引上げ（1ポイントで＋290円）を織り込むと保険料基準額は6,500円から6,800円となる。上向きの要因はいずれも国の告示・公布によるもので、資料を受領できるかどうかとは無関係に生じる。単価の置き方（確認事項No.137）のご判断を要する。自己点検7件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>44シート</t>
+          <t>84段落 17表</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>146 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2695,27 +2695,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算（9シート）。対計画比の実測、サービス別の趨勢、補正の設計とバックテスト、補正した見込量、給付費と保険料への影響、残る外れとその扱い、自己点検、確認事項。</t>
+          <t>サービス見込量の算定に関する4件の成果品を1件に束ねた統合報告書（新たに作った8シートと、4資料の全36シートの計44シート）。統合について、算定の全体像と採用案、月額への効きの統合一覧、記載事項の網羅点検、論点漏れと是正の方針、自己点検、確認事項、成果品の統合候補。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>第7期から第9期までの8年度の対計画比は、サービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満（8年平均94.93％）である。実績の伸びはサービス別に年率▲10.7％から＋28.8％まで開いており、認定者数の伸び（年率＋0.48％）とは別物である。起点と予測年数を変えた5通りのバックテストで30設定を比べ、趨勢を半分反映する置き方（φ＝0.5・上限±3％・窓5年）を選んだ。一律は30設定中15位である。補正の効きは施設・居住系を減らすかどうかで符号が変わり、月額▲58円から＋48円である。補正しても外れるサービスが6件残る。自己点検10件はいずれも適合している。</t>
+          <t>見込量算定に関する成果品が4件に分かれていたため1件に束ねた。あわせて、介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項26件に対して論点の漏れがないかを点検し、対応5件・一部対応12件・未対応9件とした。未対応の主なものは、①中長期推計が認定者数にとどまり見込量・給付費・保険料に及んでいないこと（改正法により必須の記載事項となる）、②地域支援事業が費用の額のみで量の見込みがないこと（法第117条第2項第2号）、③令和9年4月に新設される区分を見込量に立てていないこと、④供給の制約（人材）を反映していないことである。月額への効きは24件を1表に統合し、100円超が12件・50〜100円が5件・50円未満が7件である。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>44シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>146 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2733,34 +2733,34 @@
       <c r="A50" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2・表18）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り、算定の手順のチェックリスト。</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算（9シート）。対計画比の実測、サービス別の趨勢、補正の設計とバックテスト、補正した見込量、給付費と保険料への影響、残る外れとその扱い、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>本業務で確立した手順を一般化したものであり、大雪地区広域連合の計画そのものではない。同広域連合の値は適用例として明示している。方法の中心は、値を精緻にすることではなく、どの選択がどれだけ効くかを先に測り、効かないものに労力を割かないことにある。基準年度と出所を誤れば以降の精緻な作業は意味を失い、その2つが定まっていれば季節補正のような調整は誤差の範囲に収まる。</t>
+          <t>第7期から第9期までの8年度の対計画比は、サービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満（8年平均94.93％）である。実績の伸びはサービス別に年率▲10.7％から＋28.8％まで開いており、認定者数の伸び（年率＋0.48％）とは別物である。起点と予測年数を変えた5通りのバックテストで30設定を比べ、趨勢を半分反映する置き方（φ＝0.5・上限±3％・窓5年）を選んだ。一律は30設定中15位である。補正の効きは施設・居住系を減らすかどうかで符号が変わり、月額▲58円から＋48円である。補正しても外れるサービスが6件残る。自己点検10件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>197段落 18表</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2768,9 +2768,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2778,34 +2778,34 @@
       <c r="A51" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の数値が年度途中であることと、冬季と夏季の差を踏まえた補正方法の検討（9シート）。季節性の検証、令和8年度の分解、補正方法の比較と採否、施策反映の設計、施策反映の歯止め、月額への効きの一覧、自己点検、確認事項。</t>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2・表18）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り、算定の手順のチェックリスト。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>冬季と夏季の対比は、施設が＋2.80％・在宅が▲2.48％で、令和6年度・令和7年度の2年とも同じ向きに再現する。居住系と合計は測定できない。施設と在宅が逆向きであるため給付費で加重すると相殺され、年度換算係数は2.9935で一律の3.0000と0.22％しか違わない。採用パターン（令和7年度基準）は完結年度であるため季節指数の和が12となり、換算係数1.0000で季節補正は恒等的に消える。令和8年度は介護保険事業状況報告の月報により令和8年4〜7月の4か月と確定した。使いづらい主因は季節ではなく単価であり、残差は分母の採り方で＋1.63％から＋5.90％の幅がある。自己点検12件はいずれも適合している。</t>
+          <t>本業務で確立した手順を一般化したものであり、大雪地区広域連合の計画そのものではない。同広域連合の値は適用例として明示している。方法の中心は、値を精緻にすることではなく、どの選択がどれだけ効くかを先に測り、効かないものに労力を割かないことにある。基準年度と出所を誤れば以降の精緻な作業は意味を失い、その2つが定まっていれば季節補正のような調整は誤差の範囲に収まる。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>197段落 18表</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2813,9 +2813,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定について、基準年度・出所・伸ばし方の組合せごとに給付費と保険料への影響を示したもの（8シート）。基準年度の判定、出所の比較、算定パターンと妥当性、サービス見込量、給付費と保険料への影響、自己点検、確認事項。</t>
+          <t>令和8年度の数値が年度途中であることと、冬季と夏季の差を踏まえた補正方法の検討（9シート）。季節性の検証、令和8年度の分解、補正方法の比較と採否、施策反映の設計、施策反映の歯止め、月額への効きの一覧、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>数量（利用者数）の基準年度に使えるのは令和7年度だけである。令和8年度は約4か月分の実績しかなく、計画作成支援ツールの月平均利用者数は年度累計を12で除しているため令和7年度の約0.37倍の値になっている。単価（1人1月あたり給付費・利用回数）は月数に中立であり令和8年度でも使える。見える化システムの総括表は保険者単位、計画作成支援ツールは3町合計で、同じ令和7年度の利用者数でも+1.4％から+243％の開きがある。算定できた7パターンで算定上の月額基準額は6,224円から7,049円まで825円の幅がある。自己点検11件はいずれも適合している。</t>
+          <t>冬季と夏季の対比は、施設が＋2.80％・在宅が▲2.48％で、令和6年度・令和7年度の2年とも同じ向きに再現する。居住系と合計は測定できない。施設と在宅が逆向きであるため給付費で加重すると相殺され、年度換算係数は2.9935で一律の3.0000と0.22％しか違わない。採用パターン（令和7年度基準）は完結年度であるため季節指数の和が12となり、換算係数1.0000で季節補正は恒等的に消える。令和8年度は介護保険事業状況報告の月報により令和8年4〜7月の4か月と確定した。使いづらい主因は季節ではなく単価であり、残差は分母の採り方で＋1.63％から＋5.90％の幅がある。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2868,34 +2868,34 @@
       <c r="A53" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を当区域の実データと突き合わせた協議資料（10シート）。区域内の現況、論点14件の一覧と詳細、条例で定める基準の区分、令和9年4月から義務となるもの、運営推進会議の開催頻度、省令上の定員の単位、計画素案の修正、確認事項。</t>
+          <t>サービス見込量の算定について、基準年度・出所・伸ばし方の組合せごとに給付費と保険料への影響を示したもの（8シート）。基準年度の判定、出所の比較、算定パターンと妥当性、サービス見込量、給付費と保険料への影響、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>地域密着型サービスの基準は広域連合の条例で定めるものであり、省令はその条例を定めるに当たっての基準である。広域連合の指定基準条例を受領していないため、令和6年厚生労働省令第16号による改正後の省令に対応しているかを確認できていない。令和9年4月1日に義務となる協力医療機関の要件強化（10事業所）と生産性向上委員会（15事業所）も条例の対応規定を経て事業者に及ぶため、条例の確認を最も重い確認事項としている。ご指示により計画素案の本文には反映していない。ただし本作業で判明した計画素案自体の誤り3件は修正した。</t>
+          <t>数量（利用者数）の基準年度に使えるのは令和7年度だけである。令和8年度は約4か月分の実績しかなく、計画作成支援ツールの月平均利用者数は年度累計を12で除しているため令和7年度の約0.37倍の値になっている。単価（1人1月あたり給付費・利用回数）は月数に中立であり令和8年度でも使える。見える化システムの総括表は保険者単位、計画作成支援ツールは3町合計で、同じ令和7年度の利用者数でも+1.4％から+243％の開きがある。算定できた7パターンで算定上の月額基準額は6,224円から7,049円まで825円の幅がある。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>47 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2920,27 +2920,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料の内容を第10期計画に反映するための協議資料（9シート）。第9期計画における給付適正化の記載、国が求める記載事項との対照、第10期での位置づけ（3案）、主要3事業の毎年度の定量目標、財政調整交付金への影響、進捗管理の手引きに基づく整理、介護SCRの活用案、確認事項。</t>
+          <t>指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を当区域の実データと突き合わせた協議資料（10シート）。区域内の現況、論点14件の一覧と詳細、条例で定める基準の区分、令和9年4月から義務となるもの、運営推進会議の開催頻度、省令上の定員の単位、計画素案の修正、確認事項。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、「介護給付適正化計画」という語では記載がない。介護保険法第117条第2項第3号・第4号に対応する記載であり、第10期では第7期給付適正化計画に当たる。ご指示により計画素案の本文には反映していない。計画素案に入れるかどうかは第9期計画の体裁を勘案して協議する。</t>
+          <t>地域密着型サービスの基準は広域連合の条例で定めるものであり、省令はその条例を定めるに当たっての基準である。広域連合の指定基準条例を受領していないため、令和6年厚生労働省令第16号による改正後の省令に対応しているかを確認できていない。令和9年4月1日に義務となる協力医療機関の要件強化（10事業所）と生産性向上委員会（15事業所）も条例の対応規定を経て事業者に及ぶため、条例の確認を最も重い確認事項としている。ご指示により計画素案の本文には反映していない。ただし本作業で判明した計画素案自体の誤り3件は修正した。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2965,27 +2965,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
+          <t>令和8年9月10日に受領した5件の資料の内容を第10期計画に反映するための協議資料（9シート）。第9期計画における給付適正化の記載、国が求める記載事項との対照、第10期での位置づけ（3案）、主要3事業の毎年度の定量目標、財政調整交付金への影響、進捗管理の手引きに基づく整理、介護SCRの活用案、確認事項。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
+          <t>第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、「介護給付適正化計画」という語では記載がない。介護保険法第117条第2項第3号・第4号に対応する記載であり、第10期では第7期給付適正化計画に当たる。ご指示により計画素案の本文には反映していない。計画素案に入れるかどうかは第9期計画の体裁を勘案して協議する。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>119段落 17表</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -3003,34 +3003,34 @@
       <c r="A56" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
+          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
+          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>119段落 17表</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3038,9 +3038,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3055,17 +3055,17 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
+          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
+          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3083,9 +3083,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3100,27 +3100,27 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
+          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
+          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3145,27 +3145,27 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
+          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3173,9 +3173,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3190,27 +3190,27 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3235,27 +3235,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3280,17 +3280,17 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3363,34 +3363,34 @@
       <c r="A64" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3398,9 +3398,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3408,34 +3408,34 @@
       <c r="A65" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3443,9 +3443,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3460,17 +3460,17 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3488,9 +3488,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3498,34 +3498,34 @@
       <c r="A67" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>26 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -3533,9 +3533,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3550,37 +3550,37 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I68" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3595,32 +3595,32 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検（8シート）。算定式の対照、保険料の式の突合、受給率の分母の粒度による差の実測、見える化システムの画面との不一致、入力の落とし穴、作成者へ返せる情報。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>算定式の骨格は当方と同じであり、差は受給率の分母の粒度だけである。要介護度7区分（当方）と要介護・要支援の2区分（アプリ）の差は第10期3か年で月額3円、令和22年度で0.22％である。アプリの保険料の式（収納見込＝月額×補正後被保険者延人数×収納率）に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢4件はいずれも令和8年度が終期側に来るもので、令和6年度→令和7年度のみが令和8年度を含まない。作業過程の記録であり、送付資料としては用いない（内部保管）。自己点検11件はいずれも適合している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr">
@@ -3640,27 +3640,27 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検（8シート）。算定式の対照、保険料の式の突合、受給率の分母の粒度による差の実測、見える化システムの画面との不一致、入力の落とし穴、作成者へ返せる情報。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>算定式の骨格は当方と同じであり、差は受給率の分母の粒度だけである。要介護度7区分（当方）と要介護・要支援の2区分（アプリ）の差は第10期3か年で月額3円、令和22年度で0.22％である。アプリの保険料の式（収納見込＝月額×補正後被保険者延人数×収納率）に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢4件はいずれも令和8年度が終期側に来るもので、令和6年度→令和7年度のみが令和8年度を含まない。作業過程の記録であり、送付資料としては用いない（内部保管）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -3685,27 +3685,27 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>119 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -3713,9 +3713,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I71" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3723,34 +3723,34 @@
       <c r="A72" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>119 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3758,9 +3758,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3775,17 +3775,17 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
+          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>36 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -3813,34 +3813,34 @@
       <c r="A74" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>45 KB</t>
+          <t>36 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -3858,34 +3858,34 @@
       <c r="A75" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>45 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3910,27 +3910,27 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -3938,9 +3938,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I76" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3955,27 +3955,27 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -3993,34 +3993,34 @@
       <c r="A78" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -4028,9 +4028,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I78" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4045,27 +4045,27 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -4073,9 +4073,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4090,27 +4090,27 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -4118,9 +4118,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4135,27 +4135,27 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -4180,27 +4180,27 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -4225,17 +4225,17 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
@@ -4315,27 +4315,27 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -4360,27 +4360,27 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -4388,9 +4388,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4405,27 +4405,27 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
@@ -4450,27 +4450,27 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -4495,17 +4495,17 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -4540,27 +4540,27 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -4568,9 +4568,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I90" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4585,27 +4585,27 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>482段落 52表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -4613,9 +4613,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4630,27 +4630,27 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>482段落 52表</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>65 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -4675,27 +4675,27 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>65 KB</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
@@ -4720,27 +4720,27 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -4758,44 +4758,44 @@
       <c r="A95" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I95" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4810,32 +4810,32 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I96" s="12" t="inlineStr">
@@ -4855,27 +4855,27 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
@@ -4883,9 +4883,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I97" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I97" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4893,34 +4893,34 @@
       <c r="A98" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -4928,9 +4928,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4945,17 +4945,17 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
@@ -4973,9 +4973,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I99" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4983,44 +4983,44 @@
       <c r="A100" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H100" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I100" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I100" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -5035,27 +5035,27 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H101" s="18" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H102" s="18" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -5170,95 +5170,119 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H104" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I104" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="52" customHeight="1">
+      <c r="A105" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B105" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D104" s="6" t="inlineStr">
+      <c r="D105" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E105" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="F105" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G104" s="7" t="inlineStr">
+      <c r="G105" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H104" s="18" t="inlineStr">
+      <c r="H105" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I104" s="18" t="inlineStr">
+      <c r="I105" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="19" t="inlineStr">
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="28" customHeight="1">
-      <c r="A107" s="3" t="inlineStr">
+    <row r="108" ht="28" customHeight="1">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr"/>
-      <c r="E107" s="3" t="inlineStr"/>
-      <c r="F107" s="3" t="inlineStr"/>
-      <c r="G107" s="3" t="inlineStr"/>
-      <c r="H107" s="3" t="inlineStr"/>
-      <c r="I107" s="3" t="inlineStr"/>
-    </row>
-    <row r="108" ht="32" customHeight="1">
-      <c r="A108" s="5" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr"/>
+      <c r="E108" s="3" t="inlineStr"/>
+      <c r="F108" s="3" t="inlineStr"/>
+      <c r="G108" s="3" t="inlineStr"/>
+      <c r="H108" s="3" t="inlineStr"/>
+      <c r="I108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D108" s="20" t="n"/>
-      <c r="E108" s="20" t="n"/>
-      <c r="F108" s="20" t="n"/>
-      <c r="G108" s="20" t="n"/>
-      <c r="H108" s="20" t="n"/>
-      <c r="I108" s="21" t="n"/>
-    </row>
-    <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
@@ -5266,7 +5290,7 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D109" s="20" t="n"/>
@@ -5277,17 +5301,17 @@
       <c r="I109" s="21" t="n"/>
     </row>
     <row r="110" ht="32" customHeight="1">
-      <c r="A110" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A110" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B110" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、入力前段支援アプリの点検、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D110" s="20" t="n"/>
@@ -5298,17 +5322,17 @@
       <c r="I110" s="21" t="n"/>
     </row>
     <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A111" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、入力前段支援アプリの点検、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D111" s="20" t="n"/>
@@ -5319,17 +5343,17 @@
       <c r="I111" s="21" t="n"/>
     </row>
     <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A112" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B112" s="6" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、認知症施策推進計画の位置づけと見込量への反映、サービス見込量の算定_第1次概算、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D112" s="20" t="n"/>
@@ -5340,17 +5364,17 @@
       <c r="I112" s="21" t="n"/>
     </row>
     <row r="113" ht="32" customHeight="1">
-      <c r="A113" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、認知症施策推進計画の位置づけと見込量への反映、サービス見込量の算定_第1次概算、資料を受領できない場合のサービス見込量、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D113" s="20" t="n"/>
@@ -5361,17 +5385,17 @@
       <c r="I113" s="21" t="n"/>
     </row>
     <row r="114" ht="32" customHeight="1">
-      <c r="A114" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A114" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B114" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D114" s="20" t="n"/>
@@ -5382,17 +5406,17 @@
       <c r="I114" s="21" t="n"/>
     </row>
     <row r="115" ht="32" customHeight="1">
-      <c r="A115" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D115" s="20" t="n"/>
@@ -5402,18 +5426,18 @@
       <c r="H115" s="20" t="n"/>
       <c r="I115" s="21" t="n"/>
     </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B116" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="C116" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの95件、別スコープ5件</t>
+    <row r="116" ht="32" customHeight="1">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D116" s="20" t="n"/>
@@ -5423,8 +5447,29 @@
       <c r="H116" s="20" t="n"/>
       <c r="I116" s="21" t="n"/>
     </row>
-    <row r="118" ht="100" customHeight="1">
-      <c r="A118" s="23" t="inlineStr">
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B117" s="22" t="n">
+        <v>101</v>
+      </c>
+      <c r="C117" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの96件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D117" s="20" t="n"/>
+      <c r="E117" s="20" t="n"/>
+      <c r="F117" s="20" t="n"/>
+      <c r="G117" s="20" t="n"/>
+      <c r="H117" s="20" t="n"/>
+      <c r="I117" s="21" t="n"/>
+    </row>
+    <row r="119" ht="100" customHeight="1">
+      <c r="A119" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -5435,15 +5480,15 @@
     <mergeCell ref="C111:I111"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C110:I110"/>
+    <mergeCell ref="A107:I107"/>
     <mergeCell ref="C114:I114"/>
     <mergeCell ref="C113:I113"/>
+    <mergeCell ref="A119:H119"/>
     <mergeCell ref="C109:I109"/>
-    <mergeCell ref="A106:I106"/>
-    <mergeCell ref="A118:H118"/>
     <mergeCell ref="C115:I115"/>
     <mergeCell ref="C112:I112"/>
-    <mergeCell ref="C108:I108"/>
     <mergeCell ref="C116:I116"/>
+    <mergeCell ref="C117:I117"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>119 KB</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>123 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>36 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2463,34 +2463,34 @@
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイル及び画面の写し7点の受領点検（9シート）。受領資料の概要、推計誤差、認定率と在宅サービス利用率の実績、当方の分析との突合、画面の状態、推計方法の設定の現状、進めない件の切り分け、自己点検、確認事項。</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値（11シート）。この表について（暫定値である旨）、入力の順序と設定項目、認定者数、施設・居住系サービス利用者数、在宅サービス利用者数、在宅サービス利用回（日）数、実績のない区分と新設の区分、地域支援事業の見込み量、給付費と保険料、暫定値である理由、自己点検。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>4件はいずれも「推計方法の設定」画面で伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。推計誤差が算定されていないサービスは5件で、施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。認定者数の推計は、基本推計が2か年とも実績をわずかに下回り（▲0.72％・▲0.50％）、包括推計は2か年とも上回る（＋0.55％・＋1.91％）。2か年平均の絶対誤差は基本0.61％・包括1.23％。サービス別の推計誤差で±10％以上外れる6件のうち4件は、当方が対計画比の補正試算で「補正では解消しない外れ」とした6件と一致する。在宅サービス利用率は令和8年度まで出力されるが、同年度は4月から7月までの4か月であり夏季に偏る。サービス一覧に令和8年法律第51号で新設される「登録施設介護支援」が既に置かれている。画面の写しにより、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であることが確かめられた（施設・居住系7サービス16値が完全一致）。推計方法の設定は既定値のままで、総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0（ゼロ）である。画面は令和32年度まで推計する。自己点検20件はいずれも適合している。</t>
+          <t>本表の値は必要資料が未受領であることによる暫定値であり、確定値ではない。その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している。単純に四捨五入すると定期巡回・随時対応型訪問介護看護（月0.58人）のような小口のサービスが0になり、令和9年度以降も0のまま残るためである。要支援の列があるかどうかは受領した画面の写しから読み、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。自己点検17件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>51 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案（9シート）。受領資料の概要、資料の区分と取扱い、収録内容と当計画への対応、当区域の現状、KPI設計案、記録様式と集計の様式、段階的な導入と役割分担、自己点検、確認事項。</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイル及び画面の写し7点の受領点検（9シート）。受領資料の概要、推計誤差、認定率と在宅サービス利用率の実績、当方の分析との突合、画面の状態、推計方法の設定の現状、進めない件の切り分け、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>受領した5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があるため、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む2件はリポジトリに格納していない。第9期の施策2-5の指標は「会議の開催回数」であり、第9期評価で「指標不足・成果を測る指標がない」と判定している。市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを「提起された地域課題のうち翌年度の事業・予算に反映されたものの割合」（施策化への転換率）とする案とした。13指標のうち12指標は現時点で測れず、3町共通の記録様式の整備と令和9年度の基準値の把握を要する。測れている指標は交付金評価の「生活支援コーディネーターの地域ケア会議への参加割合」のみで、3町とも令和8年度に満点となっている。自己点検13件はいずれも適合している。</t>
+          <t>4件はいずれも「推計方法の設定」画面で伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。推計誤差が算定されていないサービスは5件で、施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。認定者数の推計は、基本推計が2か年とも実績をわずかに下回り（▲0.72％・▲0.50％）、包括推計は2か年とも上回る（＋0.55％・＋1.91％）。2か年平均の絶対誤差は基本0.61％・包括1.23％。サービス別の推計誤差で±10％以上外れる6件のうち4件は、当方が対計画比の補正試算で「補正では解消しない外れ」とした6件と一致する。在宅サービス利用率は令和8年度まで出力されるが、同年度は4月から7月までの4か月であり夏季に偏る。サービス一覧に令和8年法律第51号で新設される「登録施設介護支援」が既に置かれている。画面の写しにより、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であることが確かめられた（施設・居住系7サービス16値が完全一致）。推計方法の設定は既定値のままで、総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0（ゼロ）である。画面は令和32年度まで推計する。自己点検20件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2560,27 +2560,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法第13条の市町村認知症施策推進計画をどう扱うかの検討資料（10シート）。法の規定と当広域連合の関係、計画素案の現状、位置づけの3案、認知症に関する数量、交付金評価の町別、見込量算定への反映、意見聴取の設計、自己点検、確認事項。</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案（9シート）。受領資料の概要、資料の区分と取扱い、収録内容と当計画への対応、当区域の現状、KPI設計案、記録様式と集計の様式、段階的な導入と役割分担、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月16日に案Bを採用し、計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映した（新たな節・章は起こしていない）。同法の名宛人は「市町村」であり、広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体であるから、広域連合の計画に一体のものとして定めても市町村計画としての効力は生じない。構成3町がそれぞれ策定し、広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案である。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込み（前年比▲14.7％）は1事業所の定員縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。自己点検11件はいずれも適合している。</t>
+          <t>受領した5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があるため、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む2件はリポジトリに格納していない。第9期の施策2-5の指標は「会議の開催回数」であり、第9期評価で「指標不足・成果を測る指標がない」と判定している。市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを「提起された地域課題のうち翌年度の事業・予算に反映されたものの割合」（施策化への転換率）とする案とした。13指標のうち12指標は現時点で測れず、3町共通の記録様式の整備と令和9年度の基準値の把握を要する。測れている指標は交付金評価の「生活支援コーディネーターの地域ケア会議への参加割合」のみで、3町とも令和8年度に満点となっている。自己点検13件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2605,27 +2605,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>いま手元にある資料で算定できるところまで見込量を進めたもの（18シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、要介護度別の給付費、在宅と施設の連鎖、施設・居住系と必要利用定員総数、供給の制約（定員上限）と在宅への振替、地域支援事業の量と費用、中長期推計、給付費と保険料、報酬改定率の感度、据え置き・既定値の一覧、自己点検、確認事項。</t>
+          <t>共生社会の実現を推進するための認知症基本法第13条の市町村認知症施策推進計画をどう扱うかの検討資料（10シート）。法の規定と当広域連合の関係、計画素案の現状、位置づけの3案、認知症に関する数量、交付金評価の町別、見込量算定への反映、意見聴取の設計、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになった。これを基礎として、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は算定上の月額基準額で＋8円である。①利用回（日）数の見込み（法第117条第2項第1号）、②地域支援事業の量の見込み（同項第2号）、③中長期推計（令和17年度・令和22年度）の見込量・給付費、④要介護度別の給付費、⑤供給の制約（定員上限）と在宅への振替、⑥報酬改定率の感度を新たに算定し、統合報告書が未対応としていた論点のうち4件に着手した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に区域内の定員の99.9％に達し、令和17年度には超える。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現に指定を受けている定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。自己点検22件はいずれも適合している。</t>
+          <t>令和8年9月16日に案Bを採用し、計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映した（新たな節・章は起こしていない）。同法の名宛人は「市町村」であり、広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体であるから、広域連合の計画に一体のものとして定めても市町村計画としての効力は生じない。構成3町がそれぞれ策定し、広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案である。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込み（前年比▲14.7％）は1事業所の定員縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>18シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>73 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2650,27 +2650,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量（全11節・表17点）。サービス見込量29区分、利用回（日）数12区分、地域支援事業の量12項目、給付費、保険料算定表の記号A〜J、必要利用定員総数、中長期推計、据え置き23件の区分、月額基準額の幅、計画本文への注記の案。</t>
+          <t>いま手元にある資料で算定できるところまで見込量を進めたもの（18シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、要介護度別の給付費、在宅と施設の連鎖、施設・居住系と必要利用定員総数、供給の制約（定員上限）と在宅への振替、地域支援事業の量と費用、中長期推計、給付費と保険料、報酬改定率の感度、据え置き・既定値の一覧、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 第1次概算（令和8年9月16日）が、そのまま「資料が届かない前提」の見込量であることを示したもの。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円で、百円未満四捨五入した保険料基準額は6,400円となり第9期と同額である。据え置き23件を出どころで分けると、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件である。発注者・3町から追加の資料がまったく届かなくても、国の告示さえ出れば計画は確定する。ただし6,436円は据え置き前提の下限に近く、単価の趨勢（＋185〜＋374円）や報酬改定率（3％で＋182円）、第1号被保険者負担割合の引上げ（1ポイントで＋290円）を織り込むと保険料基準額は6,500円から6,800円となる。上向きの要因はいずれも国の告示・公布によるもので、資料を受領できるかどうかとは無関係に生じる。単価の置き方（確認事項No.137）のご判断を要する。自己点検7件はいずれも適合している。</t>
+          <t>令和8年9月11日に年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになった。これを基礎として、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は算定上の月額基準額で＋8円である。①利用回（日）数の見込み（法第117条第2項第1号）、②地域支援事業の量の見込み（同項第2号）、③中長期推計（令和17年度・令和22年度）の見込量・給付費、④要介護度別の給付費、⑤供給の制約（定員上限）と在宅への振替、⑥報酬改定率の感度を新たに算定し、統合報告書が未対応としていた論点のうち4件に着手した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に区域内の定員の99.9％に達し、令和17年度には超える。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現に指定を受けている定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。自己点検22件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>84段落 17表</t>
+          <t>18シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>73 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2695,27 +2695,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に関する4件の成果品を1件に束ねた統合報告書（新たに作った8シートと、4資料の全36シートの計44シート）。統合について、算定の全体像と採用案、月額への効きの統合一覧、記載事項の網羅点検、論点漏れと是正の方針、自己点検、確認事項、成果品の統合候補。</t>
+          <t>追加の資料が届かない前提でのサービス見込量（全11節・表17点）。サービス見込量29区分、利用回（日）数12区分、地域支援事業の量12項目、給付費、保険料算定表の記号A〜J、必要利用定員総数、中長期推計、据え置き23件の区分、月額基準額の幅、計画本文への注記の案。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>見込量算定に関する成果品が4件に分かれていたため1件に束ねた。あわせて、介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項26件に対して論点の漏れがないかを点検し、対応5件・一部対応12件・未対応9件とした。未対応の主なものは、①中長期推計が認定者数にとどまり見込量・給付費・保険料に及んでいないこと（改正法により必須の記載事項となる）、②地域支援事業が費用の額のみで量の見込みがないこと（法第117条第2項第2号）、③令和9年4月に新設される区分を見込量に立てていないこと、④供給の制約（人材）を反映していないことである。月額への効きは24件を1表に統合し、100円超が12件・50〜100円が5件・50円未満が7件である。自己点検12件はいずれも適合している。</t>
+          <t>サービス見込量の算定 第1次概算（令和8年9月16日）が、そのまま「資料が届かない前提」の見込量であることを示したもの。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円で、百円未満四捨五入した保険料基準額は6,400円となり第9期と同額である。据え置き23件を出どころで分けると、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件である。発注者・3町から追加の資料がまったく届かなくても、国の告示さえ出れば計画は確定する。ただし6,436円は据え置き前提の下限に近く、単価の趨勢（＋185〜＋374円）や報酬改定率（3％で＋182円）、第1号被保険者負担割合の引上げ（1ポイントで＋290円）を織り込むと保険料基準額は6,500円から6,800円となる。上向きの要因はいずれも国の告示・公布によるもので、資料を受領できるかどうかとは無関係に生じる。単価の置き方（確認事項No.137）のご判断を要する。自己点検7件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>44シート</t>
+          <t>84段落 17表</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>146 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算（9シート）。対計画比の実測、サービス別の趨勢、補正の設計とバックテスト、補正した見込量、給付費と保険料への影響、残る外れとその扱い、自己点検、確認事項。</t>
+          <t>サービス見込量の算定に関する4件の成果品を1件に束ねた統合報告書（新たに作った8シートと、4資料の全36シートの計44シート）。統合について、算定の全体像と採用案、月額への効きの統合一覧、記載事項の網羅点検、論点漏れと是正の方針、自己点検、確認事項、成果品の統合候補。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>第7期から第9期までの8年度の対計画比は、サービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満（8年平均94.93％）である。実績の伸びはサービス別に年率▲10.7％から＋28.8％まで開いており、認定者数の伸び（年率＋0.48％）とは別物である。起点と予測年数を変えた5通りのバックテストで30設定を比べ、趨勢を半分反映する置き方（φ＝0.5・上限±3％・窓5年）を選んだ。一律は30設定中15位である。補正の効きは施設・居住系を減らすかどうかで符号が変わり、月額▲58円から＋48円である。補正しても外れるサービスが6件残る。自己点検10件はいずれも適合している。</t>
+          <t>見込量算定に関する成果品が4件に分かれていたため1件に束ねた。あわせて、介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項26件に対して論点の漏れがないかを点検し、対応5件・一部対応12件・未対応9件とした。未対応の主なものは、①中長期推計が認定者数にとどまり見込量・給付費・保険料に及んでいないこと（改正法により必須の記載事項となる）、②地域支援事業が費用の額のみで量の見込みがないこと（法第117条第2項第2号）、③令和9年4月に新設される区分を見込量に立てていないこと、④供給の制約（人材）を反映していないことである。月額への効きは24件を1表に統合し、100円超が12件・50〜100円が5件・50円未満が7件である。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>44シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>146 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2778,34 +2778,34 @@
       <c r="A51" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2・表18）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り、算定の手順のチェックリスト。</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算（9シート）。対計画比の実測、サービス別の趨勢、補正の設計とバックテスト、補正した見込量、給付費と保険料への影響、残る外れとその扱い、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>本業務で確立した手順を一般化したものであり、大雪地区広域連合の計画そのものではない。同広域連合の値は適用例として明示している。方法の中心は、値を精緻にすることではなく、どの選択がどれだけ効くかを先に測り、効かないものに労力を割かないことにある。基準年度と出所を誤れば以降の精緻な作業は意味を失い、その2つが定まっていれば季節補正のような調整は誤差の範囲に収まる。</t>
+          <t>第7期から第9期までの8年度の対計画比は、サービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満（8年平均94.93％）である。実績の伸びはサービス別に年率▲10.7％から＋28.8％まで開いており、認定者数の伸び（年率＋0.48％）とは別物である。起点と予測年数を変えた5通りのバックテストで30設定を比べ、趨勢を半分反映する置き方（φ＝0.5・上限±3％・窓5年）を選んだ。一律は30設定中15位である。補正の効きは施設・居住系を減らすかどうかで符号が変わり、月額▲58円から＋48円である。補正しても外れるサービスが6件残る。自己点検10件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>197段落 18表</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2813,9 +2813,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2823,34 +2823,34 @@
       <c r="A52" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の数値が年度途中であることと、冬季と夏季の差を踏まえた補正方法の検討（9シート）。季節性の検証、令和8年度の分解、補正方法の比較と採否、施策反映の設計、施策反映の歯止め、月額への効きの一覧、自己点検、確認事項。</t>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2・表18）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り、算定の手順のチェックリスト。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>冬季と夏季の対比は、施設が＋2.80％・在宅が▲2.48％で、令和6年度・令和7年度の2年とも同じ向きに再現する。居住系と合計は測定できない。施設と在宅が逆向きであるため給付費で加重すると相殺され、年度換算係数は2.9935で一律の3.0000と0.22％しか違わない。採用パターン（令和7年度基準）は完結年度であるため季節指数の和が12となり、換算係数1.0000で季節補正は恒等的に消える。令和8年度は介護保険事業状況報告の月報により令和8年4〜7月の4か月と確定した。使いづらい主因は季節ではなく単価であり、残差は分母の採り方で＋1.63％から＋5.90％の幅がある。自己点検12件はいずれも適合している。</t>
+          <t>本業務で確立した手順を一般化したものであり、大雪地区広域連合の計画そのものではない。同広域連合の値は適用例として明示している。方法の中心は、値を精緻にすることではなく、どの選択がどれだけ効くかを先に測り、効かないものに労力を割かないことにある。基準年度と出所を誤れば以降の精緻な作業は意味を失い、その2つが定まっていれば季節補正のような調整は誤差の範囲に収まる。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>197段落 18表</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2858,9 +2858,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定について、基準年度・出所・伸ばし方の組合せごとに給付費と保険料への影響を示したもの（8シート）。基準年度の判定、出所の比較、算定パターンと妥当性、サービス見込量、給付費と保険料への影響、自己点検、確認事項。</t>
+          <t>令和8年度の数値が年度途中であることと、冬季と夏季の差を踏まえた補正方法の検討（9シート）。季節性の検証、令和8年度の分解、補正方法の比較と採否、施策反映の設計、施策反映の歯止め、月額への効きの一覧、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>数量（利用者数）の基準年度に使えるのは令和7年度だけである。令和8年度は約4か月分の実績しかなく、計画作成支援ツールの月平均利用者数は年度累計を12で除しているため令和7年度の約0.37倍の値になっている。単価（1人1月あたり給付費・利用回数）は月数に中立であり令和8年度でも使える。見える化システムの総括表は保険者単位、計画作成支援ツールは3町合計で、同じ令和7年度の利用者数でも+1.4％から+243％の開きがある。算定できた7パターンで算定上の月額基準額は6,224円から7,049円まで825円の幅がある。自己点検11件はいずれも適合している。</t>
+          <t>冬季と夏季の対比は、施設が＋2.80％・在宅が▲2.48％で、令和6年度・令和7年度の2年とも同じ向きに再現する。居住系と合計は測定できない。施設と在宅が逆向きであるため給付費で加重すると相殺され、年度換算係数は2.9935で一律の3.0000と0.22％しか違わない。採用パターン（令和7年度基準）は完結年度であるため季節指数の和が12となり、換算係数1.0000で季節補正は恒等的に消える。令和8年度は介護保険事業状況報告の月報により令和8年4〜7月の4か月と確定した。使いづらい主因は季節ではなく単価であり、残差は分母の採り方で＋1.63％から＋5.90％の幅がある。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2913,34 +2913,34 @@
       <c r="A54" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を当区域の実データと突き合わせた協議資料（10シート）。区域内の現況、論点14件の一覧と詳細、条例で定める基準の区分、令和9年4月から義務となるもの、運営推進会議の開催頻度、省令上の定員の単位、計画素案の修正、確認事項。</t>
+          <t>サービス見込量の算定について、基準年度・出所・伸ばし方の組合せごとに給付費と保険料への影響を示したもの（8シート）。基準年度の判定、出所の比較、算定パターンと妥当性、サービス見込量、給付費と保険料への影響、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>地域密着型サービスの基準は広域連合の条例で定めるものであり、省令はその条例を定めるに当たっての基準である。広域連合の指定基準条例を受領していないため、令和6年厚生労働省令第16号による改正後の省令に対応しているかを確認できていない。令和9年4月1日に義務となる協力医療機関の要件強化（10事業所）と生産性向上委員会（15事業所）も条例の対応規定を経て事業者に及ぶため、条例の確認を最も重い確認事項としている。ご指示により計画素案の本文には反映していない。ただし本作業で判明した計画素案自体の誤り3件は修正した。</t>
+          <t>数量（利用者数）の基準年度に使えるのは令和7年度だけである。令和8年度は約4か月分の実績しかなく、計画作成支援ツールの月平均利用者数は年度累計を12で除しているため令和7年度の約0.37倍の値になっている。単価（1人1月あたり給付費・利用回数）は月数に中立であり令和8年度でも使える。見える化システムの総括表は保険者単位、計画作成支援ツールは3町合計で、同じ令和7年度の利用者数でも+1.4％から+243％の開きがある。算定できた7パターンで算定上の月額基準額は6,224円から7,049円まで825円の幅がある。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>47 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2965,27 +2965,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料の内容を第10期計画に反映するための協議資料（9シート）。第9期計画における給付適正化の記載、国が求める記載事項との対照、第10期での位置づけ（3案）、主要3事業の毎年度の定量目標、財政調整交付金への影響、進捗管理の手引きに基づく整理、介護SCRの活用案、確認事項。</t>
+          <t>指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を当区域の実データと突き合わせた協議資料（10シート）。区域内の現況、論点14件の一覧と詳細、条例で定める基準の区分、令和9年4月から義務となるもの、運営推進会議の開催頻度、省令上の定員の単位、計画素案の修正、確認事項。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、「介護給付適正化計画」という語では記載がない。介護保険法第117条第2項第3号・第4号に対応する記載であり、第10期では第7期給付適正化計画に当たる。ご指示により計画素案の本文には反映していない。計画素案に入れるかどうかは第9期計画の体裁を勘案して協議する。</t>
+          <t>地域密着型サービスの基準は広域連合の条例で定めるものであり、省令はその条例を定めるに当たっての基準である。広域連合の指定基準条例を受領していないため、令和6年厚生労働省令第16号による改正後の省令に対応しているかを確認できていない。令和9年4月1日に義務となる協力医療機関の要件強化（10事業所）と生産性向上委員会（15事業所）も条例の対応規定を経て事業者に及ぶため、条例の確認を最も重い確認事項としている。ご指示により計画素案の本文には反映していない。ただし本作業で判明した計画素案自体の誤り3件は修正した。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
+          <t>令和8年9月10日に受領した5件の資料の内容を第10期計画に反映するための協議資料（9シート）。第9期計画における給付適正化の記載、国が求める記載事項との対照、第10期での位置づけ（3案）、主要3事業の毎年度の定量目標、財政調整交付金への影響、進捗管理の手引きに基づく整理、介護SCRの活用案、確認事項。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
+          <t>第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、「介護給付適正化計画」という語では記載がない。介護保険法第117条第2項第3号・第4号に対応する記載であり、第10期では第7期給付適正化計画に当たる。ご指示により計画素案の本文には反映していない。計画素案に入れるかどうかは第9期計画の体裁を勘案して協議する。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>119段落 17表</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3048,34 +3048,34 @@
       <c r="A57" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
+          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
+          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>119段落 17表</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3083,9 +3083,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3100,17 +3100,17 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
+          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
+          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3128,9 +3128,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3145,27 +3145,27 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
+          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
+          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3190,27 +3190,27 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
+          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3218,9 +3218,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3235,27 +3235,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3280,27 +3280,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3370,17 +3370,17 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3408,34 +3408,34 @@
       <c r="A65" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3443,9 +3443,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3453,34 +3453,34 @@
       <c r="A66" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3488,9 +3488,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I66" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3505,17 +3505,17 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -3533,9 +3533,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3543,34 +3543,34 @@
       <c r="A68" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3578,9 +3578,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3595,37 +3595,37 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I69" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3640,32 +3640,32 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検（8シート）。算定式の対照、保険料の式の突合、受給率の分母の粒度による差の実測、見える化システムの画面との不一致、入力の落とし穴、作成者へ返せる情報。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>算定式の骨格は当方と同じであり、差は受給率の分母の粒度だけである。要介護度7区分（当方）と要介護・要支援の2区分（アプリ）の差は第10期3か年で月額3円、令和22年度で0.22％である。アプリの保険料の式（収納見込＝月額×補正後被保険者延人数×収納率）に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢4件はいずれも令和8年度が終期側に来るもので、令和6年度→令和7年度のみが令和8年度を含まない。作業過程の記録であり、送付資料としては用いない（内部保管）。自己点検11件はいずれも適合している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I70" s="12" t="inlineStr">
@@ -3685,27 +3685,27 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検（8シート）。算定式の対照、保険料の式の突合、受給率の分母の粒度による差の実測、見える化システムの画面との不一致、入力の落とし穴、作成者へ返せる情報。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>算定式の骨格は当方と同じであり、差は受給率の分母の粒度だけである。要介護度7区分（当方）と要介護・要支援の2区分（アプリ）の差は第10期3か年で月額3円、令和22年度で0.22％である。アプリの保険料の式（収納見込＝月額×補正後被保険者延人数×収納率）に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢4件はいずれも令和8年度が終期側に来るもので、令和6年度→令和7年度のみが令和8年度を含まない。作業過程の記録であり、送付資料としては用いない（内部保管）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -3730,27 +3730,27 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>123 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3758,9 +3758,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I72" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3768,34 +3768,34 @@
       <c r="A73" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>124 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -3803,9 +3803,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3820,17 +3820,17 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
+          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -3858,34 +3858,34 @@
       <c r="A75" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>45 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3903,34 +3903,34 @@
       <c r="A76" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>45 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -3955,27 +3955,27 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -3983,9 +3983,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I77" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4000,27 +4000,27 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -4038,34 +4038,34 @@
       <c r="A79" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -4073,9 +4073,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I79" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4090,27 +4090,27 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -4118,9 +4118,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I80" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4135,27 +4135,27 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -4163,9 +4163,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4180,27 +4180,27 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -4225,27 +4225,27 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
@@ -4315,17 +4315,17 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -4360,27 +4360,27 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -4405,27 +4405,27 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
@@ -4433,9 +4433,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I87" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4450,27 +4450,27 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -4495,27 +4495,27 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -4540,17 +4540,17 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -4585,27 +4585,27 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -4613,9 +4613,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I91" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4630,27 +4630,27 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>482段落 52表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -4658,9 +4658,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I92" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4675,27 +4675,27 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>482段落 52表</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>65 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
@@ -4720,27 +4720,27 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>65 KB</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -4765,27 +4765,27 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -4803,44 +4803,44 @@
       <c r="A96" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I96" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4855,32 +4855,32 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I97" s="12" t="inlineStr">
@@ -4900,27 +4900,27 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -4928,9 +4928,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I98" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I98" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4938,34 +4938,34 @@
       <c r="A99" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
@@ -4973,9 +4973,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4990,17 +4990,17 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
@@ -5018,9 +5018,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I100" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -5028,44 +5028,44 @@
       <c r="A101" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H101" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I101" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -5080,27 +5080,27 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H102" s="18" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H103" s="18" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -5215,95 +5215,119 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H105" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I105" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="52" customHeight="1">
+      <c r="A106" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="D106" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E106" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr">
+      <c r="F106" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr">
+      <c r="G106" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H105" s="18" t="inlineStr">
+      <c r="H106" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I105" s="18" t="inlineStr">
+      <c r="I106" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="19" t="inlineStr">
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="28" customHeight="1">
-      <c r="A108" s="3" t="inlineStr">
+    <row r="109" ht="28" customHeight="1">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr"/>
-      <c r="E108" s="3" t="inlineStr"/>
-      <c r="F108" s="3" t="inlineStr"/>
-      <c r="G108" s="3" t="inlineStr"/>
-      <c r="H108" s="3" t="inlineStr"/>
-      <c r="I108" s="3" t="inlineStr"/>
-    </row>
-    <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr"/>
+      <c r="E109" s="3" t="inlineStr"/>
+      <c r="F109" s="3" t="inlineStr"/>
+      <c r="G109" s="3" t="inlineStr"/>
+      <c r="H109" s="3" t="inlineStr"/>
+      <c r="I109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D109" s="20" t="n"/>
-      <c r="E109" s="20" t="n"/>
-      <c r="F109" s="20" t="n"/>
-      <c r="G109" s="20" t="n"/>
-      <c r="H109" s="20" t="n"/>
-      <c r="I109" s="21" t="n"/>
-    </row>
-    <row r="110" ht="32" customHeight="1">
-      <c r="A110" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B110" s="6" t="n">
@@ -5311,7 +5335,7 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D110" s="20" t="n"/>
@@ -5322,17 +5346,17 @@
       <c r="I110" s="21" t="n"/>
     </row>
     <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A111" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、入力前段支援アプリの点検、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D111" s="20" t="n"/>
@@ -5343,17 +5367,17 @@
       <c r="I111" s="21" t="n"/>
     </row>
     <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A112" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B112" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、入力前段支援アプリの点検、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D112" s="20" t="n"/>
@@ -5364,17 +5388,17 @@
       <c r="I112" s="21" t="n"/>
     </row>
     <row r="113" ht="32" customHeight="1">
-      <c r="A113" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A113" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、認知症施策推進計画の位置づけと見込量への反映、サービス見込量の算定_第1次概算、資料を受領できない場合のサービス見込量、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D113" s="20" t="n"/>
@@ -5385,17 +5409,17 @@
       <c r="I113" s="21" t="n"/>
     </row>
     <row r="114" ht="32" customHeight="1">
-      <c r="A114" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B114" s="6" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、認知症施策推進計画の位置づけと見込量への反映、サービス見込量の算定_第1次概算、資料を受領できない場合のサービス見込量、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D114" s="20" t="n"/>
@@ -5406,17 +5430,17 @@
       <c r="I114" s="21" t="n"/>
     </row>
     <row r="115" ht="32" customHeight="1">
-      <c r="A115" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、見える化_見込量の入力値（暫定）、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D115" s="20" t="n"/>
@@ -5427,17 +5451,17 @@
       <c r="I115" s="21" t="n"/>
     </row>
     <row r="116" ht="32" customHeight="1">
-      <c r="A116" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B116" s="6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D116" s="20" t="n"/>
@@ -5447,18 +5471,18 @@
       <c r="H116" s="20" t="n"/>
       <c r="I116" s="21" t="n"/>
     </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B117" s="22" t="n">
-        <v>101</v>
-      </c>
-      <c r="C117" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの96件、別スコープ5件</t>
+    <row r="117" ht="32" customHeight="1">
+      <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D117" s="20" t="n"/>
@@ -5468,8 +5492,29 @@
       <c r="H117" s="20" t="n"/>
       <c r="I117" s="21" t="n"/>
     </row>
-    <row r="119" ht="100" customHeight="1">
-      <c r="A119" s="23" t="inlineStr">
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B118" s="22" t="n">
+        <v>102</v>
+      </c>
+      <c r="C118" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの97件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D118" s="20" t="n"/>
+      <c r="E118" s="20" t="n"/>
+      <c r="F118" s="20" t="n"/>
+      <c r="G118" s="20" t="n"/>
+      <c r="H118" s="20" t="n"/>
+      <c r="I118" s="21" t="n"/>
+    </row>
+    <row r="120" ht="100" customHeight="1">
+      <c r="A120" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -5480,13 +5525,13 @@
     <mergeCell ref="C111:I111"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C110:I110"/>
-    <mergeCell ref="A107:I107"/>
+    <mergeCell ref="C118:I118"/>
     <mergeCell ref="C114:I114"/>
+    <mergeCell ref="A108:I108"/>
     <mergeCell ref="C113:I113"/>
-    <mergeCell ref="A119:H119"/>
-    <mergeCell ref="C109:I109"/>
     <mergeCell ref="C115:I115"/>
     <mergeCell ref="C112:I112"/>
+    <mergeCell ref="A120:H120"/>
     <mergeCell ref="C116:I116"/>
     <mergeCell ref="C117:I117"/>
   </mergeCells>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>124 KB</t>
+          <t>126 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2470,27 +2470,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値（11シート）。この表について（暫定値である旨）、入力の順序と設定項目、認定者数、施設・居住系サービス利用者数、在宅サービス利用者数、在宅サービス利用回（日）数、実績のない区分と新設の区分、地域支援事業の見込み量、給付費と保険料、暫定値である理由、自己点検。</t>
+          <t>所得段階別第1号被保険者数の将来推計（5シート）。この表について、構成比の置き方、段階別の将来推計、補正後被保険者数の照合、自己点検。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>本表の値は必要資料が未受領であることによる暫定値であり、確定値ではない。その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している。単純に四捨五入すると定期巡回・随時対応型訪問介護看護（月0.58人）のような小口のサービスが0になり、令和9年度以降も0のまま残るためである。要支援の列があるかどうかは受領した画面の写しから読み、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。自己点検17件はいずれも適合している。</t>
+          <t>見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した（確認事項No.156）。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数0.991352と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準13段階とは異なるため、入力画面では所得段階の設定を弾力化とする。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>51 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2508,34 +2508,34 @@
       <c r="A45" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイル及び画面の写し7点の受領点検（9シート）。受領資料の概要、推計誤差、認定率と在宅サービス利用率の実績、当方の分析との突合、画面の状態、推計方法の設定の現状、進めない件の切り分け、自己点検、確認事項。</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値（11シート）。この表について（暫定値である旨）、入力の順序と設定項目、認定者数、施設・居住系サービス利用者数、在宅サービス利用者数、在宅サービス利用回（日）数、実績のない区分と新設の区分、地域支援事業の見込み量、給付費と保険料、暫定値である理由、自己点検。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>4件はいずれも「推計方法の設定」画面で伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。推計誤差が算定されていないサービスは5件で、施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。認定者数の推計は、基本推計が2か年とも実績をわずかに下回り（▲0.72％・▲0.50％）、包括推計は2か年とも上回る（＋0.55％・＋1.91％）。2か年平均の絶対誤差は基本0.61％・包括1.23％。サービス別の推計誤差で±10％以上外れる6件のうち4件は、当方が対計画比の補正試算で「補正では解消しない外れ」とした6件と一致する。在宅サービス利用率は令和8年度まで出力されるが、同年度は4月から7月までの4か月であり夏季に偏る。サービス一覧に令和8年法律第51号で新設される「登録施設介護支援」が既に置かれている。画面の写しにより、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であることが確かめられた（施設・居住系7サービス16値が完全一致）。推計方法の設定は既定値のままで、総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0（ゼロ）である。画面は令和32年度まで推計する。自己点検20件はいずれも適合している。</t>
+          <t>本表の値は必要資料が未受領であることによる暫定値であり、確定値ではない。その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している。単純に四捨五入すると定期巡回・随時対応型訪問介護看護（月0.58人）のような小口のサービスが0になり、令和9年度以降も0のまま残るためである。要支援の列があるかどうかは受領した画面の写しから読み、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。自己点検17件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>60 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案（9シート）。受領資料の概要、資料の区分と取扱い、収録内容と当計画への対応、当区域の現状、KPI設計案、記録様式と集計の様式、段階的な導入と役割分担、自己点検、確認事項。</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイル及び画面の写し7点の受領点検（9シート）。受領資料の概要、推計誤差、認定率と在宅サービス利用率の実績、当方の分析との突合、画面の状態、推計方法の設定の現状、進めない件の切り分け、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>受領した5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があるため、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む2件はリポジトリに格納していない。第9期の施策2-5の指標は「会議の開催回数」であり、第9期評価で「指標不足・成果を測る指標がない」と判定している。市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを「提起された地域課題のうち翌年度の事業・予算に反映されたものの割合」（施策化への転換率）とする案とした。13指標のうち12指標は現時点で測れず、3町共通の記録様式の整備と令和9年度の基準値の把握を要する。測れている指標は交付金評価の「生活支援コーディネーターの地域ケア会議への参加割合」のみで、3町とも令和8年度に満点となっている。自己点検13件はいずれも適合している。</t>
+          <t>4件はいずれも「推計方法の設定」画面で伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。推計誤差が算定されていないサービスは5件で、施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。認定者数の推計は、基本推計が2か年とも実績をわずかに下回り（▲0.72％・▲0.50％）、包括推計は2か年とも上回る（＋0.55％・＋1.91％）。2か年平均の絶対誤差は基本0.61％・包括1.23％。サービス別の推計誤差で±10％以上外れる6件のうち4件は、当方が対計画比の補正試算で「補正では解消しない外れ」とした6件と一致する。在宅サービス利用率は令和8年度まで出力されるが、同年度は4月から7月までの4か月であり夏季に偏る。サービス一覧に令和8年法律第51号で新設される「登録施設介護支援」が既に置かれている。画面の写しにより、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であることが確かめられた（施設・居住系7サービス16値が完全一致）。推計方法の設定は既定値のままで、総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0（ゼロ）である。画面は令和32年度まで推計する。自己点検20件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2605,27 +2605,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法第13条の市町村認知症施策推進計画をどう扱うかの検討資料（10シート）。法の規定と当広域連合の関係、計画素案の現状、位置づけの3案、認知症に関する数量、交付金評価の町別、見込量算定への反映、意見聴取の設計、自己点検、確認事項。</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案（9シート）。受領資料の概要、資料の区分と取扱い、収録内容と当計画への対応、当区域の現状、KPI設計案、記録様式と集計の様式、段階的な導入と役割分担、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月16日に案Bを採用し、計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映した（新たな節・章は起こしていない）。同法の名宛人は「市町村」であり、広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体であるから、広域連合の計画に一体のものとして定めても市町村計画としての効力は生じない。構成3町がそれぞれ策定し、広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案である。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込み（前年比▲14.7％）は1事業所の定員縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。自己点検11件はいずれも適合している。</t>
+          <t>受領した5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があるため、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む2件はリポジトリに格納していない。第9期の施策2-5の指標は「会議の開催回数」であり、第9期評価で「指標不足・成果を測る指標がない」と判定している。市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを「提起された地域課題のうち翌年度の事業・予算に反映されたものの割合」（施策化への転換率）とする案とした。13指標のうち12指標は現時点で測れず、3町共通の記録様式の整備と令和9年度の基準値の把握を要する。測れている指標は交付金評価の「生活支援コーディネーターの地域ケア会議への参加割合」のみで、3町とも令和8年度に満点となっている。自己点検13件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2650,27 +2650,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>いま手元にある資料で算定できるところまで見込量を進めたもの（18シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、要介護度別の給付費、在宅と施設の連鎖、施設・居住系と必要利用定員総数、供給の制約（定員上限）と在宅への振替、地域支援事業の量と費用、中長期推計、給付費と保険料、報酬改定率の感度、据え置き・既定値の一覧、自己点検、確認事項。</t>
+          <t>共生社会の実現を推進するための認知症基本法第13条の市町村認知症施策推進計画をどう扱うかの検討資料（10シート）。法の規定と当広域連合の関係、計画素案の現状、位置づけの3案、認知症に関する数量、交付金評価の町別、見込量算定への反映、意見聴取の設計、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになった。これを基礎として、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は算定上の月額基準額で＋8円である。①利用回（日）数の見込み（法第117条第2項第1号）、②地域支援事業の量の見込み（同項第2号）、③中長期推計（令和17年度・令和22年度）の見込量・給付費、④要介護度別の給付費、⑤供給の制約（定員上限）と在宅への振替、⑥報酬改定率の感度を新たに算定し、統合報告書が未対応としていた論点のうち4件に着手した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に区域内の定員の99.9％に達し、令和17年度には超える。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現に指定を受けている定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。自己点検22件はいずれも適合している。</t>
+          <t>令和8年9月16日に案Bを採用し、計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映した（新たな節・章は起こしていない）。同法の名宛人は「市町村」であり、広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体であるから、広域連合の計画に一体のものとして定めても市町村計画としての効力は生じない。構成3町がそれぞれ策定し、広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案である。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込み（前年比▲14.7％）は1事業所の定員縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>18シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>73 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2695,27 +2695,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量（全11節・表17点）。サービス見込量29区分、利用回（日）数12区分、地域支援事業の量12項目、給付費、保険料算定表の記号A〜J、必要利用定員総数、中長期推計、据え置き23件の区分、月額基準額の幅、計画本文への注記の案。</t>
+          <t>いま手元にある資料で算定できるところまで見込量を進めたもの（18シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、要介護度別の給付費、在宅と施設の連鎖、施設・居住系と必要利用定員総数、供給の制約（定員上限）と在宅への振替、地域支援事業の量と費用、中長期推計、給付費と保険料、報酬改定率の感度、据え置き・既定値の一覧、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 第1次概算（令和8年9月16日）が、そのまま「資料が届かない前提」の見込量であることを示したもの。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円で、百円未満四捨五入した保険料基準額は6,400円となり第9期と同額である。据え置き23件を出どころで分けると、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件である。発注者・3町から追加の資料がまったく届かなくても、国の告示さえ出れば計画は確定する。ただし6,436円は据え置き前提の下限に近く、単価の趨勢（＋185〜＋374円）や報酬改定率（3％で＋182円）、第1号被保険者負担割合の引上げ（1ポイントで＋290円）を織り込むと保険料基準額は6,500円から6,800円となる。上向きの要因はいずれも国の告示・公布によるもので、資料を受領できるかどうかとは無関係に生じる。単価の置き方（確認事項No.137）のご判断を要する。自己点検7件はいずれも適合している。</t>
+          <t>令和8年9月11日に年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになった。これを基礎として、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は算定上の月額基準額で＋8円である。①利用回（日）数の見込み（法第117条第2項第1号）、②地域支援事業の量の見込み（同項第2号）、③中長期推計（令和17年度・令和22年度）の見込量・給付費、④要介護度別の給付費、⑤供給の制約（定員上限）と在宅への振替、⑥報酬改定率の感度を新たに算定し、統合報告書が未対応としていた論点のうち4件に着手した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に区域内の定員の99.9％に達し、令和17年度には超える。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現に指定を受けている定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。自己点検22件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>84段落 17表</t>
+          <t>18シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>75 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に関する4件の成果品を1件に束ねた統合報告書（新たに作った8シートと、4資料の全36シートの計44シート）。統合について、算定の全体像と採用案、月額への効きの統合一覧、記載事項の網羅点検、論点漏れと是正の方針、自己点検、確認事項、成果品の統合候補。</t>
+          <t>追加の資料が届かない前提でのサービス見込量（全11節・表17点）。サービス見込量29区分、利用回（日）数12区分、地域支援事業の量12項目、給付費、保険料算定表の記号A〜J、必要利用定員総数、中長期推計、据え置き23件の区分、月額基準額の幅、計画本文への注記の案。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>見込量算定に関する成果品が4件に分かれていたため1件に束ねた。あわせて、介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項26件に対して論点の漏れがないかを点検し、対応5件・一部対応12件・未対応9件とした。未対応の主なものは、①中長期推計が認定者数にとどまり見込量・給付費・保険料に及んでいないこと（改正法により必須の記載事項となる）、②地域支援事業が費用の額のみで量の見込みがないこと（法第117条第2項第2号）、③令和9年4月に新設される区分を見込量に立てていないこと、④供給の制約（人材）を反映していないことである。月額への効きは24件を1表に統合し、100円超が12件・50〜100円が5件・50円未満が7件である。自己点検12件はいずれも適合している。</t>
+          <t>サービス見込量の算定 第1次概算（令和8年9月16日）が、そのまま「資料が届かない前提」の見込量であることを示したもの。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円で、百円未満四捨五入した保険料基準額は6,400円となり第9期と同額である。据え置き23件を出どころで分けると、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件である。発注者・3町から追加の資料がまったく届かなくても、国の告示さえ出れば計画は確定する。ただし6,436円は据え置き前提の下限に近く、単価の趨勢（＋185〜＋374円）や報酬改定率（3％で＋182円）、第1号被保険者負担割合の引上げ（1ポイントで＋290円）を織り込むと保険料基準額は6,500円から6,800円となる。上向きの要因はいずれも国の告示・公布によるもので、資料を受領できるかどうかとは無関係に生じる。単価の置き方（確認事項No.137）のご判断を要する。自己点検7件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>44シート</t>
+          <t>84段落 17表</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>146 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2785,27 +2785,27 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算（9シート）。対計画比の実測、サービス別の趨勢、補正の設計とバックテスト、補正した見込量、給付費と保険料への影響、残る外れとその扱い、自己点検、確認事項。</t>
+          <t>サービス見込量の算定に関する4件の成果品を1件に束ねた統合報告書（新たに作った8シートと、4資料の全36シートの計44シート）。統合について、算定の全体像と採用案、月額への効きの統合一覧、記載事項の網羅点検、論点漏れと是正の方針、自己点検、確認事項、成果品の統合候補。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>第7期から第9期までの8年度の対計画比は、サービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満（8年平均94.93％）である。実績の伸びはサービス別に年率▲10.7％から＋28.8％まで開いており、認定者数の伸び（年率＋0.48％）とは別物である。起点と予測年数を変えた5通りのバックテストで30設定を比べ、趨勢を半分反映する置き方（φ＝0.5・上限±3％・窓5年）を選んだ。一律は30設定中15位である。補正の効きは施設・居住系を減らすかどうかで符号が変わり、月額▲58円から＋48円である。補正しても外れるサービスが6件残る。自己点検10件はいずれも適合している。</t>
+          <t>見込量算定に関する成果品が4件に分かれていたため1件に束ねた。あわせて、介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項26件に対して論点の漏れがないかを点検し、対応5件・一部対応12件・未対応9件とした。未対応の主なものは、①中長期推計が認定者数にとどまり見込量・給付費・保険料に及んでいないこと（改正法により必須の記載事項となる）、②地域支援事業が費用の額のみで量の見込みがないこと（法第117条第2項第2号）、③令和9年4月に新設される区分を見込量に立てていないこと、④供給の制約（人材）を反映していないことである。月額への効きは24件を1表に統合し、100円超が12件・50〜100円が5件・50円未満が7件である。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>44シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>146 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2823,34 +2823,34 @@
       <c r="A52" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2・表18）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り、算定の手順のチェックリスト。</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算（9シート）。対計画比の実測、サービス別の趨勢、補正の設計とバックテスト、補正した見込量、給付費と保険料への影響、残る外れとその扱い、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>本業務で確立した手順を一般化したものであり、大雪地区広域連合の計画そのものではない。同広域連合の値は適用例として明示している。方法の中心は、値を精緻にすることではなく、どの選択がどれだけ効くかを先に測り、効かないものに労力を割かないことにある。基準年度と出所を誤れば以降の精緻な作業は意味を失い、その2つが定まっていれば季節補正のような調整は誤差の範囲に収まる。</t>
+          <t>第7期から第9期までの8年度の対計画比は、サービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満（8年平均94.93％）である。実績の伸びはサービス別に年率▲10.7％から＋28.8％まで開いており、認定者数の伸び（年率＋0.48％）とは別物である。起点と予測年数を変えた5通りのバックテストで30設定を比べ、趨勢を半分反映する置き方（φ＝0.5・上限±3％・窓5年）を選んだ。一律は30設定中15位である。補正の効きは施設・居住系を減らすかどうかで符号が変わり、月額▲58円から＋48円である。補正しても外れるサービスが6件残る。自己点検10件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>197段落 18表</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2858,9 +2858,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2868,34 +2868,34 @@
       <c r="A53" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の数値が年度途中であることと、冬季と夏季の差を踏まえた補正方法の検討（9シート）。季節性の検証、令和8年度の分解、補正方法の比較と採否、施策反映の設計、施策反映の歯止め、月額への効きの一覧、自己点検、確認事項。</t>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2・表18）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り、算定の手順のチェックリスト。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>冬季と夏季の対比は、施設が＋2.80％・在宅が▲2.48％で、令和6年度・令和7年度の2年とも同じ向きに再現する。居住系と合計は測定できない。施設と在宅が逆向きであるため給付費で加重すると相殺され、年度換算係数は2.9935で一律の3.0000と0.22％しか違わない。採用パターン（令和7年度基準）は完結年度であるため季節指数の和が12となり、換算係数1.0000で季節補正は恒等的に消える。令和8年度は介護保険事業状況報告の月報により令和8年4〜7月の4か月と確定した。使いづらい主因は季節ではなく単価であり、残差は分母の採り方で＋1.63％から＋5.90％の幅がある。自己点検12件はいずれも適合している。</t>
+          <t>本業務で確立した手順を一般化したものであり、大雪地区広域連合の計画そのものではない。同広域連合の値は適用例として明示している。方法の中心は、値を精緻にすることではなく、どの選択がどれだけ効くかを先に測り、効かないものに労力を割かないことにある。基準年度と出所を誤れば以降の精緻な作業は意味を失い、その2つが定まっていれば季節補正のような調整は誤差の範囲に収まる。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>197段落 18表</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2903,9 +2903,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2920,27 +2920,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定について、基準年度・出所・伸ばし方の組合せごとに給付費と保険料への影響を示したもの（8シート）。基準年度の判定、出所の比較、算定パターンと妥当性、サービス見込量、給付費と保険料への影響、自己点検、確認事項。</t>
+          <t>令和8年度の数値が年度途中であることと、冬季と夏季の差を踏まえた補正方法の検討（9シート）。季節性の検証、令和8年度の分解、補正方法の比較と採否、施策反映の設計、施策反映の歯止め、月額への効きの一覧、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>数量（利用者数）の基準年度に使えるのは令和7年度だけである。令和8年度は約4か月分の実績しかなく、計画作成支援ツールの月平均利用者数は年度累計を12で除しているため令和7年度の約0.37倍の値になっている。単価（1人1月あたり給付費・利用回数）は月数に中立であり令和8年度でも使える。見える化システムの総括表は保険者単位、計画作成支援ツールは3町合計で、同じ令和7年度の利用者数でも+1.4％から+243％の開きがある。算定できた7パターンで算定上の月額基準額は6,224円から7,049円まで825円の幅がある。自己点検11件はいずれも適合している。</t>
+          <t>冬季と夏季の対比は、施設が＋2.80％・在宅が▲2.48％で、令和6年度・令和7年度の2年とも同じ向きに再現する。居住系と合計は測定できない。施設と在宅が逆向きであるため給付費で加重すると相殺され、年度換算係数は2.9935で一律の3.0000と0.22％しか違わない。採用パターン（令和7年度基準）は完結年度であるため季節指数の和が12となり、換算係数1.0000で季節補正は恒等的に消える。令和8年度は介護保険事業状況報告の月報により令和8年4〜7月の4か月と確定した。使いづらい主因は季節ではなく単価であり、残差は分母の採り方で＋1.63％から＋5.90％の幅がある。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2958,34 +2958,34 @@
       <c r="A55" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を当区域の実データと突き合わせた協議資料（10シート）。区域内の現況、論点14件の一覧と詳細、条例で定める基準の区分、令和9年4月から義務となるもの、運営推進会議の開催頻度、省令上の定員の単位、計画素案の修正、確認事項。</t>
+          <t>サービス見込量の算定について、基準年度・出所・伸ばし方の組合せごとに給付費と保険料への影響を示したもの（8シート）。基準年度の判定、出所の比較、算定パターンと妥当性、サービス見込量、給付費と保険料への影響、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>地域密着型サービスの基準は広域連合の条例で定めるものであり、省令はその条例を定めるに当たっての基準である。広域連合の指定基準条例を受領していないため、令和6年厚生労働省令第16号による改正後の省令に対応しているかを確認できていない。令和9年4月1日に義務となる協力医療機関の要件強化（10事業所）と生産性向上委員会（15事業所）も条例の対応規定を経て事業者に及ぶため、条例の確認を最も重い確認事項としている。ご指示により計画素案の本文には反映していない。ただし本作業で判明した計画素案自体の誤り3件は修正した。</t>
+          <t>数量（利用者数）の基準年度に使えるのは令和7年度だけである。令和8年度は約4か月分の実績しかなく、計画作成支援ツールの月平均利用者数は年度累計を12で除しているため令和7年度の約0.37倍の値になっている。単価（1人1月あたり給付費・利用回数）は月数に中立であり令和8年度でも使える。見える化システムの総括表は保険者単位、計画作成支援ツールは3町合計で、同じ令和7年度の利用者数でも+1.4％から+243％の開きがある。算定できた7パターンで算定上の月額基準額は6,224円から7,049円まで825円の幅がある。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>47 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料の内容を第10期計画に反映するための協議資料（9シート）。第9期計画における給付適正化の記載、国が求める記載事項との対照、第10期での位置づけ（3案）、主要3事業の毎年度の定量目標、財政調整交付金への影響、進捗管理の手引きに基づく整理、介護SCRの活用案、確認事項。</t>
+          <t>指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を当区域の実データと突き合わせた協議資料（10シート）。区域内の現況、論点14件の一覧と詳細、条例で定める基準の区分、令和9年4月から義務となるもの、運営推進会議の開催頻度、省令上の定員の単位、計画素案の修正、確認事項。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、「介護給付適正化計画」という語では記載がない。介護保険法第117条第2項第3号・第4号に対応する記載であり、第10期では第7期給付適正化計画に当たる。ご指示により計画素案の本文には反映していない。計画素案に入れるかどうかは第9期計画の体裁を勘案して協議する。</t>
+          <t>地域密着型サービスの基準は広域連合の条例で定めるものであり、省令はその条例を定めるに当たっての基準である。広域連合の指定基準条例を受領していないため、令和6年厚生労働省令第16号による改正後の省令に対応しているかを確認できていない。令和9年4月1日に義務となる協力医療機関の要件強化（10事業所）と生産性向上委員会（15事業所）も条例の対応規定を経て事業者に及ぶため、条例の確認を最も重い確認事項としている。ご指示により計画素案の本文には反映していない。ただし本作業で判明した計画素案自体の誤り3件は修正した。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3055,27 +3055,27 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
+          <t>令和8年9月10日に受領した5件の資料の内容を第10期計画に反映するための協議資料（9シート）。第9期計画における給付適正化の記載、国が求める記載事項との対照、第10期での位置づけ（3案）、主要3事業の毎年度の定量目標、財政調整交付金への影響、進捗管理の手引きに基づく整理、介護SCRの活用案、確認事項。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
+          <t>第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、「介護給付適正化計画」という語では記載がない。介護保険法第117条第2項第3号・第4号に対応する記載であり、第10期では第7期給付適正化計画に当たる。ご指示により計画素案の本文には反映していない。計画素案に入れるかどうかは第9期計画の体裁を勘案して協議する。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>119段落 17表</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3093,34 +3093,34 @@
       <c r="A58" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
+          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
+          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>119段落 17表</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3128,9 +3128,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3145,17 +3145,17 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
+          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
+          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3173,9 +3173,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3190,27 +3190,27 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
+          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
+          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3235,27 +3235,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
+          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3263,9 +3263,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3280,27 +3280,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3325,27 +3325,27 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3370,17 +3370,17 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3415,17 +3415,17 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3453,34 +3453,34 @@
       <c r="A66" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3488,9 +3488,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3498,34 +3498,34 @@
       <c r="A67" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -3533,9 +3533,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3550,17 +3550,17 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3578,9 +3578,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3588,34 +3588,34 @@
       <c r="A69" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -3623,9 +3623,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3640,37 +3640,37 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I70" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3685,32 +3685,32 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検（8シート）。算定式の対照、保険料の式の突合、受給率の分母の粒度による差の実測、見える化システムの画面との不一致、入力の落とし穴、作成者へ返せる情報。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>算定式の骨格は当方と同じであり、差は受給率の分母の粒度だけである。要介護度7区分（当方）と要介護・要支援の2区分（アプリ）の差は第10期3か年で月額3円、令和22年度で0.22％である。アプリの保険料の式（収納見込＝月額×補正後被保険者延人数×収納率）に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢4件はいずれも令和8年度が終期側に来るもので、令和6年度→令和7年度のみが令和8年度を含まない。作業過程の記録であり、送付資料としては用いない（内部保管）。自己点検11件はいずれも適合している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
@@ -3730,27 +3730,27 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検（8シート）。算定式の対照、保険料の式の突合、受給率の分母の粒度による差の実測、見える化システムの画面との不一致、入力の落とし穴、作成者へ返せる情報。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>算定式の骨格は当方と同じであり、差は受給率の分母の粒度だけである。要介護度7区分（当方）と要介護・要支援の2区分（アプリ）の差は第10期3か年で月額3円、令和22年度で0.22％である。アプリの保険料の式（収納見込＝月額×補正後被保険者延人数×収納率）に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢4件はいずれも令和8年度が終期側に来るもので、令和6年度→令和7年度のみが令和8年度を含まない。作業過程の記録であり、送付資料としては用いない（内部保管）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3775,27 +3775,27 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>126 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -3803,9 +3803,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I73" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3813,34 +3813,34 @@
       <c r="A74" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>127 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -3848,9 +3848,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3865,17 +3865,17 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
+          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3903,34 +3903,34 @@
       <c r="A76" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>45 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -3948,34 +3948,34 @@
       <c r="A77" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>45 KB</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -4000,27 +4000,27 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -4028,9 +4028,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I78" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4045,27 +4045,27 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -4083,34 +4083,34 @@
       <c r="A80" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -4118,9 +4118,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I80" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4135,27 +4135,27 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -4163,9 +4163,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I81" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4180,27 +4180,27 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -4208,9 +4208,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I82" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4225,27 +4225,27 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -4270,27 +4270,27 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
@@ -4315,17 +4315,17 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -4360,17 +4360,17 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -4405,27 +4405,27 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
@@ -4450,27 +4450,27 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -4478,9 +4478,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4495,27 +4495,27 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -4540,27 +4540,27 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -4585,17 +4585,17 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -4630,27 +4630,27 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -4658,9 +4658,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I92" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4675,27 +4675,27 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>482段落 52表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
@@ -4703,9 +4703,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I93" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4720,27 +4720,27 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>482段落 52表</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>65 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -4765,27 +4765,27 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>65 KB</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -4810,27 +4810,27 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_アンケート調査の分析_令和8年9月業務報告.docx</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>業務仕様書「４．業務内容（3）実施済み調査結果の集計・分析」及び「５．履行工程　令和8年9月」に対する報告（全8節）。令和8年9月に行ったこと、対象4調査と回収の状況、健康とくらしの調査の結果と計画素案への反映、調査結果と保険者の実績の突合、主要所見の反映状況、調査結果の限界と留保、ご判断をお願いする事項、成果品を収める。</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>集計・クロス集計・分析は4調査とも完了している。9月に新たにできるようになったのは、年報（令和7年度）の要介護度別の明細を収めたことにより調査の結果と保険者の実績を突き合わせられるようになったことである。①在宅生活改善調査は在宅の認定者を代表せず（要介護度分布のχ²＝43.5・自由度6・1％点16.81）、「在宅で困難を抱える方の状況」として引く。②居所変更実態調査の在籍者と年報の受給者は数える対象が違い、介護老人保健施設だけが在籍＞受給である。件数・区分・留保・所見は成果品の実物から読み、見込量は見込量算定（第1次概算）を読んでいるため計画素案 第6章と同じ値になる。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>78段落 10表</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>45 KB</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -4848,44 +4848,44 @@
       <c r="A97" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I97" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4893,34 +4893,34 @@
       <c r="A98" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -4928,9 +4928,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I98" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4945,37 +4945,37 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
-        </is>
-      </c>
-      <c r="I99" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I99" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4983,34 +4983,34 @@
       <c r="A100" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
@@ -5018,9 +5018,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I100" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -5028,34 +5028,34 @@
       <c r="A101" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
@@ -5063,9 +5063,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I101" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -5073,44 +5073,44 @@
       <c r="A102" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H102" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I102" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>18 KB</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -5118,44 +5118,44 @@
       <c r="A103" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
-        </is>
-      </c>
-      <c r="H103" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I103" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I103" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -5170,27 +5170,27 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H104" s="18" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H105" s="18" t="inlineStr">
@@ -5260,124 +5260,172 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H106" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I106" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="52" customHeight="1">
+      <c r="A107" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H107" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I107" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="52" customHeight="1">
+      <c r="A108" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="D108" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E108" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr">
+      <c r="F108" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G106" s="7" t="inlineStr">
+      <c r="G108" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H106" s="18" t="inlineStr">
+      <c r="H108" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I106" s="18" t="inlineStr">
+      <c r="I108" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="19" t="inlineStr">
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="28" customHeight="1">
-      <c r="A109" s="3" t="inlineStr">
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr"/>
-      <c r="E109" s="3" t="inlineStr"/>
-      <c r="F109" s="3" t="inlineStr"/>
-      <c r="G109" s="3" t="inlineStr"/>
-      <c r="H109" s="3" t="inlineStr"/>
-      <c r="I109" s="3" t="inlineStr"/>
-    </row>
-    <row r="110" ht="32" customHeight="1">
-      <c r="A110" s="5" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr"/>
+      <c r="E111" s="3" t="inlineStr"/>
+      <c r="F111" s="3" t="inlineStr"/>
+      <c r="G111" s="3" t="inlineStr"/>
+      <c r="H111" s="3" t="inlineStr"/>
+      <c r="I111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112" ht="32" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
         </is>
       </c>
-      <c r="B110" s="6" t="n">
+      <c r="B112" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="C112" s="6" t="inlineStr">
         <is>
           <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D110" s="20" t="n"/>
-      <c r="E110" s="20" t="n"/>
-      <c r="F110" s="20" t="n"/>
-      <c r="G110" s="20" t="n"/>
-      <c r="H110" s="20" t="n"/>
-      <c r="I110" s="21" t="n"/>
-    </row>
-    <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
-        </is>
-      </c>
-      <c r="D111" s="20" t="n"/>
-      <c r="E111" s="20" t="n"/>
-      <c r="F111" s="20" t="n"/>
-      <c r="G111" s="20" t="n"/>
-      <c r="H111" s="20" t="n"/>
-      <c r="I111" s="21" t="n"/>
-    </row>
-    <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、入力前段支援アプリの点検、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D112" s="20" t="n"/>
@@ -5388,17 +5436,17 @@
       <c r="I112" s="21" t="n"/>
     </row>
     <row r="113" ht="32" customHeight="1">
-      <c r="A113" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A113" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D113" s="20" t="n"/>
@@ -5409,17 +5457,17 @@
       <c r="I113" s="21" t="n"/>
     </row>
     <row r="114" ht="32" customHeight="1">
-      <c r="A114" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A114" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B114" s="6" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、認知症施策推進計画の位置づけと見込量への反映、サービス見込量の算定_第1次概算、資料を受領できない場合のサービス見込量、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、入力前段支援アプリの点検、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D114" s="20" t="n"/>
@@ -5430,17 +5478,17 @@
       <c r="I114" s="21" t="n"/>
     </row>
     <row r="115" ht="32" customHeight="1">
-      <c r="A115" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A115" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、見える化_見込量の入力値（暫定）、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D115" s="20" t="n"/>
@@ -5451,17 +5499,17 @@
       <c r="I115" s="21" t="n"/>
     </row>
     <row r="116" ht="32" customHeight="1">
-      <c r="A116" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B116" s="6" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、認知症施策推進計画の位置づけと見込量への反映、サービス見込量の算定_第1次概算、資料を受領できない場合のサービス見込量、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、アンケート調査の分析_令和8年9月業務報告、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D116" s="20" t="n"/>
@@ -5472,17 +5520,17 @@
       <c r="I116" s="21" t="n"/>
     </row>
     <row r="117" ht="32" customHeight="1">
-      <c r="A117" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A117" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、所得段階別第1号被保険者数の将来推計、見える化_見込量の入力値（暫定）、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D117" s="20" t="n"/>
@@ -5492,18 +5540,18 @@
       <c r="H117" s="20" t="n"/>
       <c r="I117" s="21" t="n"/>
     </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B118" s="22" t="n">
-        <v>102</v>
-      </c>
-      <c r="C118" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの97件、別スコープ5件</t>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D118" s="20" t="n"/>
@@ -5513,8 +5561,50 @@
       <c r="H118" s="20" t="n"/>
       <c r="I118" s="21" t="n"/>
     </row>
-    <row r="120" ht="100" customHeight="1">
-      <c r="A120" s="23" t="inlineStr">
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+        </is>
+      </c>
+      <c r="D119" s="20" t="n"/>
+      <c r="E119" s="20" t="n"/>
+      <c r="F119" s="20" t="n"/>
+      <c r="G119" s="20" t="n"/>
+      <c r="H119" s="20" t="n"/>
+      <c r="I119" s="21" t="n"/>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B120" s="22" t="n">
+        <v>104</v>
+      </c>
+      <c r="C120" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの99件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D120" s="20" t="n"/>
+      <c r="E120" s="20" t="n"/>
+      <c r="F120" s="20" t="n"/>
+      <c r="G120" s="20" t="n"/>
+      <c r="H120" s="20" t="n"/>
+      <c r="I120" s="21" t="n"/>
+    </row>
+    <row r="122" ht="100" customHeight="1">
+      <c r="A122" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -5522,16 +5612,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C111:I111"/>
+    <mergeCell ref="C119:I119"/>
+    <mergeCell ref="A122:H122"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="C110:I110"/>
     <mergeCell ref="C118:I118"/>
     <mergeCell ref="C114:I114"/>
-    <mergeCell ref="A108:I108"/>
     <mergeCell ref="C113:I113"/>
+    <mergeCell ref="A110:I110"/>
     <mergeCell ref="C115:I115"/>
     <mergeCell ref="C112:I112"/>
-    <mergeCell ref="A120:H120"/>
+    <mergeCell ref="C120:I120"/>
     <mergeCell ref="C116:I116"/>
     <mergeCell ref="C117:I117"/>
   </mergeCells>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -4815,22 +4815,22 @@
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>業務仕様書「４．業務内容（3）実施済み調査結果の集計・分析」及び「５．履行工程　令和8年9月」に対する報告（全8節）。令和8年9月に行ったこと、対象4調査と回収の状況、健康とくらしの調査の結果と計画素案への反映、調査結果と保険者の実績の突合、主要所見の反映状況、調査結果の限界と留保、ご判断をお願いする事項、成果品を収める。</t>
+          <t>業務仕様書「４．業務内容（3）実施済み調査結果の集計・分析」及び「５．履行工程　令和8年9月」に対する報告（全11節）。令和8年9月に行ったこと、仕様書４（3）の作業項目7件に対する状況、対象4調査の母数と回収の状況、前回調査との比較（経年）、健康とくらしの調査の結果と計画素案への反映、調査結果と保険者の実績の突合、調査から把握した地域課題、主要所見の反映状況、調査結果の限界と留保、ご判断をお願いする事項、成果品を収める。</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>集計・クロス集計・分析は4調査とも完了している。9月に新たにできるようになったのは、年報（令和7年度）の要介護度別の明細を収めたことにより調査の結果と保険者の実績を突き合わせられるようになったことである。①在宅生活改善調査は在宅の認定者を代表せず（要介護度分布のχ²＝43.5・自由度6・1％点16.81）、「在宅で困難を抱える方の状況」として引く。②居所変更実態調査の在籍者と年報の受給者は数える対象が違い、介護老人保健施設だけが在籍＞受給である。件数・区分・留保・所見は成果品の実物から読み、見込量は見込量算定（第1次概算）を読んでいるため計画素案 第6章と同じ値になる。自己点検11件はいずれも適合している。</t>
+          <t>集計・クロス集計・分析は4調査とも完了している。9月に新たにできるようになったのは、年報（令和7年度）の要介護度別の明細を収めたことにより調査の結果と保険者の実績を突き合わせられるようになったことである。①在宅生活改善調査は在宅の認定者を代表せず（要介護度分布のχ²＝43.5・自由度6・1％点16.81）、「在宅で困難を抱える方の状況」として引く。②居所変更実態調査の在籍者と年報の受給者は数える対象が違い、介護老人保健施設だけが在籍＞受給である。認定を受けながらいずれのサービスも利用していない方が認定者の4分の1（486人・24.5％）を占めることを課題として掲げた。件数・区分・留保・所見・課題の根拠は成果品の実物から読み、見込量は見込量算定（第1次概算）を読んでいるため計画素案 第6章と同じ値になる。自己点検21件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>78段落 10表</t>
+          <t>121段落 16表</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>45 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（896段落143表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（923段落145表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>896段落 143表</t>
+          <t>923段落 145表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>121段落 16表</t>
+          <t>130段落 16表</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（896段落143表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（923段落145表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,17 +770,17 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（923段落145表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（925段落145表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>923段落 145表</t>
+          <t>925段落 145表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2.5 MB</t>
+          <t>2.6 MB</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>130段落 16表</t>
+          <t>137段落 16表</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（923段落145表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（925段落145表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3155,17 +3155,17 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
+          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,741市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（925段落145表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（926段落145表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>925段落 145表</t>
+          <t>926段落 145表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議の確認事項③への回答。4項目とも削除せずに算定できる見込みであり、H07は健康とくらしの調査で3.4％、H08は同8.7％、H12は在宅生活改善調査の新規提案で20.4％、H16は業務継続計画未策定減算の算定状況による。05シートに3町ヒアリングで確認することを町別に整理している。</t>
+          <t>キックオフ会議の確認事項③への回答。4項目とも削除せずに算定できる見込みであり、H07は健康とくらしの調査で3.4％、H08は同8.7％、H12は在宅生活改善調査の新規提案で20.2％、H16は業務継続計画未策定減算の算定状況による。05シートに3町ヒアリングで確認することを町別に整理している。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>49 KB</t>
+          <t>48 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>27件を照会先別に整理し、事業者への照会は5先に一本化した。未回答時の扱いを5類型（重複計上・回答の偏り・地区が不明・施設の未回答・見える化との不一致）で事前に定めている。確定値表10件のうち確定は2件（訪問介護員等181人、H12の20.4％）で、この2件は照会の結果によらず変わらない。確定後に更新する箇所11件を一覧化した。</t>
+          <t>27件を照会先別に整理し、事業者への照会は5先に一本化した。未回答時の扱いを5類型（重複計上・回答の偏り・地区が不明・施設の未回答・見える化との不一致）で事前に定めている。確定値表10件のうち確定は2件（訪問介護員等181人、H12の20.2％）で、この2件は照会の結果によらず変わらない。確定後に更新する箇所11件を一覧化した。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>51 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>36 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>127 KB</t>
+          <t>129 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>65 KB</t>
+          <t>66 KB</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（925段落145表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（926段落145表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -4735,7 +4735,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>482段落 52表</t>
+          <t>486段落 52表</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>66 KB</t>
+          <t>68 KB</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -4825,7 +4825,7 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>137段落 16表</t>
+          <t>135段落 16表</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>75 KB</t>
+          <t>76 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>146 KB</t>
+          <t>147 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（926段落145表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（928段落145表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>926段落 145表</t>
+          <t>928段落 145表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>45 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（926段落145表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（928段落145表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -4830,7 +4830,7 @@
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>129 KB</t>
+          <t>132 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>36 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>132 KB</t>
+          <t>133 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>133 KB</t>
+          <t>134 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>134 KB</t>
+          <t>137 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>137 KB</t>
+          <t>138 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>138 KB</t>
+          <t>139 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（928段落145表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（943段落147表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>928段落 145表</t>
+          <t>943段落 147表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>76 KB</t>
+          <t>77 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>139 KB</t>
+          <t>140 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>38 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（928段落145表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（943段落147表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（943段落147表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（916段落141表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>943段落 147表</t>
+          <t>916段落 141表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>36 KB</t>
+          <t>38 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（943段落147表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（916段落141表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（916段落141表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（927段落143表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>916段落 141表</t>
+          <t>927段落 143表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（916段落141表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（927段落143表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（927段落143表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（928段落143表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>927段落 143表</t>
+          <t>928段落 143表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（927段落143表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（928段落143表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>140 KB</t>
+          <t>141 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -2530,12 +2530,12 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>13シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>60 KB</t>
+          <t>68 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>141 KB</t>
+          <t>143 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 第1次概算（令和8年9月16日）が、そのまま「資料が届かない前提」の見込量であることを示したもの。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円で、百円未満四捨五入した保険料基準額は6,400円となり第9期と同額である。据え置き23件を出どころで分けると、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件である。発注者・3町から追加の資料がまったく届かなくても、国の告示さえ出れば計画は確定する。ただし6,436円は据え置き前提の下限に近く、単価の趨勢（＋185〜＋374円）や報酬改定率（3％で＋182円）、第1号被保険者負担割合の引上げ（1ポイントで＋290円）を織り込むと保険料基準額は6,500円から6,800円となる。上向きの要因はいずれも国の告示・公布によるもので、資料を受領できるかどうかとは無関係に生じる。単価の置き方（確認事項No.137）のご判断を要する。自己点検7件はいずれも適合している。</t>
+          <t>サービス見込量の算定 第1次概算（令和8年9月16日）が、そのまま「資料が届かない前提」の見込量であることを示したもの。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円で、百円未満四捨五入した保険料基準額は6,400円となり第9期と同額である。据え置き23件を出どころで分けると、令和8年10月1日に受託者の側で確定したもの2件、受託者の側で確定できるもの2件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件である。発注者・3町から追加の資料がまったく届かなくても、国の告示さえ出れば計画は確定する。ただし6,438円は据え置き前提の下限に近く、単価の趨勢（＋185〜＋374円）や報酬改定率（3％で＋182円）、第1号被保険者負担割合の引上げ（1ポイントで＋290円）を織り込むと保険料基準額は6,500円から6,800円となる。上向きの要因はいずれも国の告示・公布によるもので、資料を受領できるかどうかとは無関係に生じる。単価の置き方（確認事項No.137）のご判断を要する。自己点検7件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>84段落 17表</t>
+          <t>87段落 18表</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>143 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I122"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（928段落143表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（951段落146表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>928段落 143表</t>
+          <t>951段落 146表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>68 KB</t>
+          <t>69 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>いま手元にある資料で算定できるところまで見込量を進めたもの（18シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、要介護度別の給付費、在宅と施設の連鎖、施設・居住系と必要利用定員総数、供給の制約（定員上限）と在宅への振替、地域支援事業の量と費用、中長期推計、給付費と保険料、報酬改定率の感度、据え置き・既定値の一覧、自己点検、確認事項。</t>
+          <t>令和8年9月26日に提示した第1次概算の版（18シート）。提示した時点の値を残すため、以後は作り直していない。算定を改めた後の値は「第10期計画_サービス見込量の算定.xlsx」による。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになった。これを基礎として、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は算定上の月額基準額で＋8円である。①利用回（日）数の見込み（法第117条第2項第1号）、②地域支援事業の量の見込み（同項第2号）、③中長期推計（令和17年度・令和22年度）の見込量・給付費、④要介護度別の給付費、⑤供給の制約（定員上限）と在宅への振替、⑥報酬改定率の感度を新たに算定し、統合報告書が未対応としていた論点のうち4件に着手した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に区域内の定員の99.9％に達し、令和17年度には超える。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現に指定を受けている定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。自己点検22件はいずれも適合している。</t>
+          <t>提示した時点の総給付費は9,031,900,444円、算定上の月額基準額は6,436円、保険料基準額は6,400円である。第2次概算との差分は「第10期計画_サービス見込量の算定_第2次概算.xlsx」に掲げている。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>77 KB</t>
+          <t>76 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>提示済み（令和8年9月26日・凍結）</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr">
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_サービス見込量の算定.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量（全11節・表17点）。サービス見込量29区分、利用回（日）数12区分、地域支援事業の量12項目、給付費、保険料算定表の記号A〜J、必要利用定員総数、中長期推計、据え置き23件の区分、月額基準額の幅、計画本文への注記の案。</t>
+          <t>いま手元にある資料で算定できるところまで見込量を進めたもの（18シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、要介護度別の給付費、在宅と施設の連鎖、施設・居住系と必要利用定員総数、供給の制約（定員上限）と在宅への振替、地域支援事業の量と費用、中長期推計、給付費と保険料、報酬改定率の感度、据え置き・既定値の一覧、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 第1次概算（令和8年9月16日）が、そのまま「資料が届かない前提」の見込量であることを示したもの。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円で、百円未満四捨五入した保険料基準額は6,400円となり第9期と同額である。据え置き23件を出どころで分けると、令和8年10月1日に受託者の側で確定したもの2件、受託者の側で確定できるもの2件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件である。発注者・3町から追加の資料がまったく届かなくても、国の告示さえ出れば計画は確定する。ただし6,438円は据え置き前提の下限に近く、単価の趨勢（＋185〜＋374円）や報酬改定率（3％で＋182円）、第1号被保険者負担割合の引上げ（1ポイントで＋290円）を織り込むと保険料基準額は6,500円から6,800円となる。上向きの要因はいずれも国の告示・公布によるもので、資料を受領できるかどうかとは無関係に生じる。単価の置き方（確認事項No.137）のご判断を要する。自己点検7件はいずれも適合している。</t>
+          <t>令和8年9月11日に年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになった。これを基礎として、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は算定上の月額基準額で＋8円である。①利用回（日）数の見込み（法第117条第2項第1号）、②地域支援事業の量の見込み（同項第2号）、③中長期推計（令和17年度・令和22年度）の見込量・給付費、④要介護度別の給付費、⑤供給の制約（定員上限）と在宅への振替、⑥報酬改定率の感度を新たに算定し、統合報告書が未対応としていた論点のうち4件に着手した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に区域内の定員の99.9％に達し、令和17年度には超える。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現に指定を受けている定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。自己点検22件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>87段落 18表</t>
+          <t>18シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>77 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2785,32 +2785,32 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_第2次概算.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に関する4件の成果品を1件に束ねた統合報告書（新たに作った8シートと、4資料の全36シートの計44シート）。統合について、算定の全体像と採用案、月額への効きの統合一覧、記載事項の網羅点検、論点漏れと是正の方針、自己点検、確認事項、成果品の統合候補。</t>
+          <t>第2次概算（令和8年10月30日）の組立て（12シート）。第1次概算からの差分、保険料算定表の記号A〜Jの対照、サービス見込量・利用回（日）数・給付費の種別ごとの差分、中長期推計、月額を動かす前提、見える化システムの出力との対照、残る未決と既定値、10月30日までに行うこと、自己点検。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>見込量算定に関する成果品が4件に分かれていたため1件に束ねた。あわせて、介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項26件に対して論点の漏れがないかを点検し、対応5件・一部対応12件・未対応9件とした。未対応の主なものは、①中長期推計が認定者数にとどまり見込量・給付費・保険料に及んでいないこと（改正法により必須の記載事項となる）、②地域支援事業が費用の額のみで量の見込みがないこと（法第117条第2項第2号）、③令和9年4月に新設される区分を見込量に立てていないこと、④供給の制約（人材）を反映していないことである。月額への効きは24件を1表に統合し、100円超が12件・50〜100円が5件・50円未満が7件である。自己点検12件はいずれも適合している。</t>
+          <t>第1次概算から算定が動いた事項は、要介護度別の単価の採用と1人1月あたり利用回（日）数の要介護度別化である。総給付費は9,031,900,444円から9,035,114,142円へ、算定上の月額基準額は6,436円から6,438円へ動き、保険料基準額は6,400円で変わらない。既定値（決着しない場合の扱い）によって算定しており、ご決定をいただいた事項は令和8年10月30日の再算定で置き換わる。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>44シート</t>
+          <t>13シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>147 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>組立て（令和8年10月1日時点）</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算（9シート）。対計画比の実測、サービス別の趨勢、補正の設計とバックテスト、補正した見込量、給付費と保険料への影響、残る外れとその扱い、自己点検、確認事項。</t>
+          <t>追加の資料が届かない前提でのサービス見込量（全11節・表17点）。サービス見込量29区分、利用回（日）数12区分、地域支援事業の量12項目、給付費、保険料算定表の記号A〜J、必要利用定員総数、中長期推計、据え置き23件の区分、月額基準額の幅、計画本文への注記の案。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>第7期から第9期までの8年度の対計画比は、サービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満（8年平均94.93％）である。実績の伸びはサービス別に年率▲10.7％から＋28.8％まで開いており、認定者数の伸び（年率＋0.48％）とは別物である。起点と予測年数を変えた5通りのバックテストで30設定を比べ、趨勢を半分反映する置き方（φ＝0.5・上限±3％・窓5年）を選んだ。一律は30設定中15位である。補正の効きは施設・居住系を減らすかどうかで符号が変わり、月額▲58円から＋48円である。補正しても外れるサービスが6件残る。自己点検10件はいずれも適合している。</t>
+          <t>サービス見込量の算定 第1次概算（令和8年9月16日）が、そのまま「資料が届かない前提」の見込量であることを示したもの。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円で、百円未満四捨五入した保険料基準額は6,400円となり第9期と同額である。据え置き23件を出どころで分けると、令和8年10月1日に受託者の側で確定したもの2件、受託者の側で確定できるもの2件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件である。発注者・3町から追加の資料がまったく届かなくても、国の告示さえ出れば計画は確定する。ただし6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定率（3％で＋182円）、第1号被保険者負担割合の引上げ（1ポイントで＋290円）を織り込むと保険料基準額は6,500円から6,800円となる。上向きの要因はいずれも国の告示・公布によるもので、資料を受領できるかどうかとは無関係に生じる。単価の置き方（確認事項No.137）のご判断を要する。自己点検7件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>87段落 17表</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2868,34 +2868,34 @@
       <c r="A53" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2・表18）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り、算定の手順のチェックリスト。</t>
+          <t>サービス見込量の算定に関する4件の成果品を1件に束ねた統合報告書（新たに作った8シートと、4資料の全36シートの計44シート）。統合について、算定の全体像と採用案、月額への効きの統合一覧、記載事項の網羅点検、論点漏れと是正の方針、自己点検、確認事項、成果品の統合候補。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>本業務で確立した手順を一般化したものであり、大雪地区広域連合の計画そのものではない。同広域連合の値は適用例として明示している。方法の中心は、値を精緻にすることではなく、どの選択がどれだけ効くかを先に測り、効かないものに労力を割かないことにある。基準年度と出所を誤れば以降の精緻な作業は意味を失い、その2つが定まっていれば季節補正のような調整は誤差の範囲に収まる。</t>
+          <t>見込量算定に関する成果品が4件に分かれていたため1件に束ねた。あわせて、介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項26件に対して論点の漏れがないかを点検し、対応5件・一部対応12件・未対応9件とした。未対応の主なものは、①中長期推計が認定者数にとどまり見込量・給付費・保険料に及んでいないこと（改正法により必須の記載事項となる）、②地域支援事業が費用の額のみで量の見込みがないこと（法第117条第2項第2号）、③令和9年4月に新設される区分を見込量に立てていないこと、④供給の制約（人材）を反映していないことである。月額への効きは24件を1表に統合し、100円超が12件・50〜100円が5件・50円未満が7件である。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>197段落 18表</t>
+          <t>44シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>147 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2903,9 +2903,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2920,17 +2920,17 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の数値が年度途中であることと、冬季と夏季の差を踏まえた補正方法の検討（9シート）。季節性の検証、令和8年度の分解、補正方法の比較と採否、施策反映の設計、施策反映の歯止め、月額への効きの一覧、自己点検、確認事項。</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算（9シート）。対計画比の実測、サービス別の趨勢、補正の設計とバックテスト、補正した見込量、給付費と保険料への影響、残る外れとその扱い、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>冬季と夏季の対比は、施設が＋2.80％・在宅が▲2.48％で、令和6年度・令和7年度の2年とも同じ向きに再現する。居住系と合計は測定できない。施設と在宅が逆向きであるため給付費で加重すると相殺され、年度換算係数は2.9935で一律の3.0000と0.22％しか違わない。採用パターン（令和7年度基準）は完結年度であるため季節指数の和が12となり、換算係数1.0000で季節補正は恒等的に消える。令和8年度は介護保険事業状況報告の月報により令和8年4〜7月の4か月と確定した。使いづらい主因は季節ではなく単価であり、残差は分母の採り方で＋1.63％から＋5.90％の幅がある。自己点検12件はいずれも適合している。</t>
+          <t>第7期から第9期までの8年度の対計画比は、サービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満（8年平均94.93％）である。実績の伸びはサービス別に年率▲10.7％から＋28.8％まで開いており、認定者数の伸び（年率＋0.48％）とは別物である。起点と予測年数を変えた5通りのバックテストで30設定を比べ、趨勢を半分反映する置き方（φ＝0.5・上限±3％・窓5年）を選んだ。一律は30設定中15位である。補正の効きは施設・居住系を減らすかどうかで符号が変わり、月額▲58円から＋48円である。補正しても外れるサービスが6件残る。自己点検10件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2958,34 +2958,34 @@
       <c r="A55" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定について、基準年度・出所・伸ばし方の組合せごとに給付費と保険料への影響を示したもの（8シート）。基準年度の判定、出所の比較、算定パターンと妥当性、サービス見込量、給付費と保険料への影響、自己点検、確認事項。</t>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2・表18）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り、算定の手順のチェックリスト。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>数量（利用者数）の基準年度に使えるのは令和7年度だけである。令和8年度は約4か月分の実績しかなく、計画作成支援ツールの月平均利用者数は年度累計を12で除しているため令和7年度の約0.37倍の値になっている。単価（1人1月あたり給付費・利用回数）は月数に中立であり令和8年度でも使える。見える化システムの総括表は保険者単位、計画作成支援ツールは3町合計で、同じ令和7年度の利用者数でも+1.4％から+243％の開きがある。算定できた7パターンで算定上の月額基準額は6,224円から7,049円まで825円の幅がある。自己点検11件はいずれも適合している。</t>
+          <t>本業務で確立した手順を一般化したものであり、大雪地区広域連合の計画そのものではない。同広域連合の値は適用例として明示している。方法の中心は、値を精緻にすることではなく、どの選択がどれだけ効くかを先に測り、効かないものに労力を割かないことにある。基準年度と出所を誤れば以降の精緻な作業は意味を失い、その2つが定まっていれば季節補正のような調整は誤差の範囲に収まる。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>197段落 18表</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -2993,9 +2993,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3003,34 +3003,34 @@
       <c r="A56" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を当区域の実データと突き合わせた協議資料（10シート）。区域内の現況、論点14件の一覧と詳細、条例で定める基準の区分、令和9年4月から義務となるもの、運営推進会議の開催頻度、省令上の定員の単位、計画素案の修正、確認事項。</t>
+          <t>令和8年度の数値が年度途中であることと、冬季と夏季の差を踏まえた補正方法の検討（9シート）。季節性の検証、令和8年度の分解、補正方法の比較と採否、施策反映の設計、施策反映の歯止め、月額への効きの一覧、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>地域密着型サービスの基準は広域連合の条例で定めるものであり、省令はその条例を定めるに当たっての基準である。広域連合の指定基準条例を受領していないため、令和6年厚生労働省令第16号による改正後の省令に対応しているかを確認できていない。令和9年4月1日に義務となる協力医療機関の要件強化（10事業所）と生産性向上委員会（15事業所）も条例の対応規定を経て事業者に及ぶため、条例の確認を最も重い確認事項としている。ご指示により計画素案の本文には反映していない。ただし本作業で判明した計画素案自体の誤り3件は修正した。</t>
+          <t>冬季と夏季の対比は、施設が＋2.80％・在宅が▲2.48％で、令和6年度・令和7年度の2年とも同じ向きに再現する。居住系と合計は測定できない。施設と在宅が逆向きであるため給付費で加重すると相殺され、年度換算係数は2.9935で一律の3.0000と0.22％しか違わない。採用パターン（令和7年度基準）は完結年度であるため季節指数の和が12となり、換算係数1.0000で季節補正は恒等的に消える。令和8年度は介護保険事業状況報告の月報により令和8年4〜7月の4か月と確定した。使いづらい主因は季節ではなく単価であり、残差は分母の採り方で＋1.63％から＋5.90％の幅がある。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>47 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3048,34 +3048,34 @@
       <c r="A57" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料の内容を第10期計画に反映するための協議資料（9シート）。第9期計画における給付適正化の記載、国が求める記載事項との対照、第10期での位置づけ（3案）、主要3事業の毎年度の定量目標、財政調整交付金への影響、進捗管理の手引きに基づく整理、介護SCRの活用案、確認事項。</t>
+          <t>サービス見込量の算定について、基準年度・出所・伸ばし方の組合せごとに給付費と保険料への影響を示したもの（8シート）。基準年度の判定、出所の比較、算定パターンと妥当性、サービス見込量、給付費と保険料への影響、自己点検、確認事項。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、「介護給付適正化計画」という語では記載がない。介護保険法第117条第2項第3号・第4号に対応する記載であり、第10期では第7期給付適正化計画に当たる。ご指示により計画素案の本文には反映していない。計画素案に入れるかどうかは第9期計画の体裁を勘案して協議する。</t>
+          <t>数量（利用者数）の基準年度に使えるのは令和7年度だけである。令和8年度は約4か月分の実績しかなく、計画作成支援ツールの月平均利用者数は年度累計を12で除しているため令和7年度の約0.37倍の値になっている。単価（1人1月あたり給付費・利用回数）は月数に中立であり令和8年度でも使える。見える化システムの総括表は保険者単位、計画作成支援ツールは3町合計で、同じ令和7年度の利用者数でも+1.4％から+243％の開きがある。算定できた7パターンで算定上の月額基準額は6,224円から7,049円まで825円の幅がある。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3100,27 +3100,27 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
+          <t>指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を当区域の実データと突き合わせた協議資料（10シート）。区域内の現況、論点14件の一覧と詳細、条例で定める基準の区分、令和9年4月から義務となるもの、運営推進会議の開催頻度、省令上の定員の単位、計画素案の修正、確認事項。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
+          <t>地域密着型サービスの基準は広域連合の条例で定めるものであり、省令はその条例を定めるに当たっての基準である。広域連合の指定基準条例を受領していないため、令和6年厚生労働省令第16号による改正後の省令に対応しているかを確認できていない。令和9年4月1日に義務となる協力医療機関の要件強化（10事業所）と生産性向上委員会（15事業所）も条例の対応規定を経て事業者に及ぶため、条例の確認を最も重い確認事項としている。ご指示により計画素案の本文には反映していない。ただし本作業で判明した計画素案自体の誤り3件は修正した。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>119段落 17表</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3138,34 +3138,34 @@
       <c r="A59" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
+          <t>令和8年9月10日に受領した5件の資料の内容を第10期計画に反映するための協議資料（9シート）。第9期計画における給付適正化の記載、国が求める記載事項との対照、第10期での位置づけ（3案）、主要3事業の毎年度の定量目標、財政調整交付金への影響、進捗管理の手引きに基づく整理、介護SCRの活用案、確認事項。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,741市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
+          <t>第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、「介護給付適正化計画」という語では記載がない。介護保険法第117条第2項第3号・第4号に対応する記載であり、第10期では第7期給付適正化計画に当たる。ご指示により計画素案の本文には反映していない。計画素案に入れるかどうかは第9期計画の体裁を勘案して協議する。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3173,9 +3173,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3183,34 +3183,34 @@
       <c r="A60" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
+          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
+          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>119段落 17表</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3235,27 +3235,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
+          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
+          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,741市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3263,9 +3263,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3280,27 +3280,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
+          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
+          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3308,9 +3308,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I62" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3325,17 +3325,17 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3353,9 +3353,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3370,27 +3370,27 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3415,27 +3415,27 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3460,17 +3460,17 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3498,34 +3498,34 @@
       <c r="A67" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -3533,9 +3533,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3550,27 +3550,27 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3588,34 +3588,34 @@
       <c r="A69" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -3633,34 +3633,34 @@
       <c r="A70" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -3678,44 +3678,44 @@
       <c r="A71" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I71" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3730,27 +3730,27 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検（8シート）。算定式の対照、保険料の式の突合、受給率の分母の粒度による差の実測、見える化システムの画面との不一致、入力の落とし穴、作成者へ返せる情報。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>算定式の骨格は当方と同じであり、差は受給率の分母の粒度だけである。要介護度7区分（当方）と要介護・要支援の2区分（アプリ）の差は第10期3か年で月額3円、令和22年度で0.22％である。アプリの保険料の式（収納見込＝月額×補正後被保険者延人数×収納率）に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢4件はいずれも令和8年度が終期側に来るもので、令和6年度→令和7年度のみが令和8年度を含まない。作業過程の記録であり、送付資料としては用いない（内部保管）。自己点検11件はいずれも適合している。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3758,9 +3758,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I72" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3775,32 +3775,32 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
@@ -3820,27 +3820,27 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検（8シート）。算定式の対照、保険料の式の突合、受給率の分母の粒度による差の実測、見える化システムの画面との不一致、入力の落とし穴、作成者へ返せる情報。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>算定式の骨格は当方と同じであり、差は受給率の分母の粒度だけである。要介護度7区分（当方）と要介護・要支援の2区分（アプリ）の差は第10期3か年で月額3円、令和22年度で0.22％である。アプリの保険料の式（収納見込＝月額×補正後被保険者延人数×収納率）に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢4件はいずれも令和8年度が終期側に来るもので、令和6年度→令和7年度のみが令和8年度を含まない。作業過程の記録であり、送付資料としては用いない（内部保管）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -3848,9 +3848,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I74" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3858,34 +3858,34 @@
       <c r="A75" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3893,9 +3893,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I75" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3903,34 +3903,34 @@
       <c r="A76" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度（月額＋185〜＋374円）である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>38 KB</t>
+          <t>151 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -3938,9 +3938,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3948,34 +3948,34 @@
       <c r="A77" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理（9シート）。</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>スクリプト数・成果品の区分・確認事項の件数は実物又はソースから数えている。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件・関連が4件ある。見込量算定の統合報告書が掲げた統合候補7群の状況も示した（実施済み1・未実施5・対象外1）。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計527人）と年報（保険者単位480.17人）で9.8％違う。役割を終えた成果品13件と、算定又は記述に誤りがあり正したもの10件を発見の経緯と再発を防ぐ手立てとともに記録している。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>47 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -3993,34 +3993,34 @@
       <c r="A78" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理（9シート）。</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中しており、必要利用定員総数（確認事項No.88）が決まらないことによる。第1次概算（9月26日）を止めている確認事項の全件について、決着しない場合の当方の扱い（既定値）を置いた。効きが最も大きいのは1人1月あたり給付費の年度である。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している（第2章第4節は健康とくらしの調査の結果が本文に入っていない）。自己点検13件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -4038,34 +4038,34 @@
       <c r="A79" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -4073,9 +4073,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I79" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4090,27 +4090,27 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -4118,9 +4118,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I80" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4128,34 +4128,34 @@
       <c r="A81" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -4163,9 +4163,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I81" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4173,34 +4173,34 @@
       <c r="A82" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -4208,9 +4208,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I82" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I82" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4225,27 +4225,27 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合（10シート）。</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5・自由度6。1％点16.81）。要介護3が期待の2.8倍・要支援1が0.16倍で、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍206人＞受給134.1人／月である。特別養護老人ホーム等は受給197.5人／月が回答施設の定員152人を上回る。区域を越えた施設利用が双方向に成立しており、必要利用定員総数は区域内の施設の定員とは別に整理を要する。アンケート関係の成果品7件のうち6件を再出力した状況も収めた（残る1件は個票を読むため再実行できない）。自己点検11件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -4270,27 +4270,27 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
@@ -4298,9 +4298,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4315,27 +4315,27 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -4360,27 +4360,27 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -4405,17 +4405,17 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
@@ -4450,27 +4450,27 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -4495,27 +4495,27 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -4523,9 +4523,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4540,27 +4540,27 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -4568,9 +4568,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I90" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4585,27 +4585,27 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -4630,27 +4630,27 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -4675,27 +4675,27 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
@@ -4703,9 +4703,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I93" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4720,27 +4720,27 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>486段落 52表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -4765,27 +4765,27 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>68 KB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -4793,9 +4793,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I95" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -4810,27 +4810,27 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の分析_令和8年9月業務報告.docx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>業務仕様書「４．業務内容（3）実施済み調査結果の集計・分析」及び「５．履行工程　令和8年9月」に対する報告（全11節）。令和8年9月に行ったこと、仕様書４（3）の作業項目7件に対する状況、対象4調査の母数と回収の状況、前回調査との比較（経年）、健康とくらしの調査の結果と計画素案への反映、調査結果と保険者の実績の突合、調査から把握した地域課題、主要所見の反映状況、調査結果の限界と留保、ご判断をお願いする事項、成果品を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>集計・クロス集計・分析は4調査とも完了している。9月に新たにできるようになったのは、年報（令和7年度）の要介護度別の明細を収めたことにより調査の結果と保険者の実績を突き合わせられるようになったことである。①在宅生活改善調査は在宅の認定者を代表せず（要介護度分布のχ²＝43.5・自由度6・1％点16.81）、「在宅で困難を抱える方の状況」として引く。②居所変更実態調査の在籍者と年報の受給者は数える対象が違い、介護老人保健施設だけが在籍＞受給である。認定を受けながらいずれのサービスも利用していない方が認定者の4分の1（486人・24.5％）を占めることを課題として掲げた。件数・区分・留保・所見・課題の根拠は成果品の実物から読み、見込量は見込量算定（第1次概算）を読んでいるため計画素案 第6章と同じ値になる。自己点検21件はいずれも適合している。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>135段落 16表</t>
+          <t>486段落 52表</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -4855,27 +4855,27 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>68 KB</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
@@ -4900,27 +4900,27 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_アンケート調査の分析_令和8年9月業務報告.docx</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>業務仕様書「４．業務内容（3）実施済み調査結果の集計・分析」及び「５．履行工程　令和8年9月」に対する報告（全11節）。令和8年9月に行ったこと、仕様書４（3）の作業項目7件に対する状況、対象4調査の母数と回収の状況、前回調査との比較（経年）、健康とくらしの調査の結果と計画素案への反映、調査結果と保険者の実績の突合、調査から把握した地域課題、主要所見の反映状況、調査結果の限界と留保、ご判断をお願いする事項、成果品を収める。</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>集計・クロス集計・分析は4調査とも完了している。9月に新たにできるようになったのは、年報（令和7年度）の要介護度別の明細を収めたことにより調査の結果と保険者の実績を突き合わせられるようになったことである。①在宅生活改善調査は在宅の認定者を代表せず（要介護度分布のχ²＝43.5・自由度6・1％点16.81）、「在宅で困難を抱える方の状況」として引く。②居所変更実態調査の在籍者と年報の受給者は数える対象が違い、介護老人保健施設だけが在籍＞受給である。認定を受けながらいずれのサービスも利用していない方が認定者の4分の1（486人・24.5％）を占めることを課題として掲げた。件数・区分・留保・所見・課題の根拠は成果品の実物から読み、見込量は見込量算定（第1次概算）を読んでいるため計画素案 第6章と同じ値になる。自己点検21件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>135段落 16表</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -4938,44 +4938,44 @@
       <c r="A99" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I99" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -4983,34 +4983,34 @@
       <c r="A100" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
@@ -5018,9 +5018,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I100" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -5035,37 +5035,37 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
-        </is>
-      </c>
-      <c r="I101" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -5073,34 +5073,34 @@
       <c r="A102" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
@@ -5108,9 +5108,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I102" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -5118,34 +5118,34 @@
       <c r="A103" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
@@ -5153,9 +5153,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I103" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -5163,44 +5163,44 @@
       <c r="A104" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H104" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I104" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>18 KB</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -5208,44 +5208,44 @@
       <c r="A105" s="4" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B105" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
-        </is>
-      </c>
-      <c r="H105" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I105" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I105" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -5260,27 +5260,27 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H106" s="18" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H107" s="18" t="inlineStr">
@@ -5350,124 +5350,172 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H108" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I108" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="52" customHeight="1">
+      <c r="A109" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H109" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I109" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="52" customHeight="1">
+      <c r="A110" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="D110" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E110" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
+      <c r="F110" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G108" s="7" t="inlineStr">
+      <c r="G110" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H108" s="18" t="inlineStr">
+      <c r="H110" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I108" s="18" t="inlineStr">
+      <c r="I110" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="19" t="inlineStr">
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="A111" s="3" t="inlineStr">
+    <row r="113" ht="28" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr"/>
-      <c r="E111" s="3" t="inlineStr"/>
-      <c r="F111" s="3" t="inlineStr"/>
-      <c r="G111" s="3" t="inlineStr"/>
-      <c r="H111" s="3" t="inlineStr"/>
-      <c r="I111" s="3" t="inlineStr"/>
-    </row>
-    <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr"/>
+      <c r="E113" s="3" t="inlineStr"/>
+      <c r="F113" s="3" t="inlineStr"/>
+      <c r="G113" s="3" t="inlineStr"/>
+      <c r="H113" s="3" t="inlineStr"/>
+      <c r="I113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114" ht="32" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
         </is>
       </c>
-      <c r="B112" s="6" t="n">
+      <c r="B114" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C112" s="6" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D112" s="20" t="n"/>
-      <c r="E112" s="20" t="n"/>
-      <c r="F112" s="20" t="n"/>
-      <c r="G112" s="20" t="n"/>
-      <c r="H112" s="20" t="n"/>
-      <c r="I112" s="21" t="n"/>
-    </row>
-    <row r="113" ht="32" customHeight="1">
-      <c r="A113" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
-        </is>
-      </c>
-      <c r="D113" s="20" t="n"/>
-      <c r="E113" s="20" t="n"/>
-      <c r="F113" s="20" t="n"/>
-      <c r="G113" s="20" t="n"/>
-      <c r="H113" s="20" t="n"/>
-      <c r="I113" s="21" t="n"/>
-    </row>
-    <row r="114" ht="32" customHeight="1">
-      <c r="A114" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、入力前段支援アプリの点検、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D114" s="20" t="n"/>
@@ -5478,17 +5526,17 @@
       <c r="I114" s="21" t="n"/>
     </row>
     <row r="115" ht="32" customHeight="1">
-      <c r="A115" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A115" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D115" s="20" t="n"/>
@@ -5499,17 +5547,17 @@
       <c r="I115" s="21" t="n"/>
     </row>
     <row r="116" ht="32" customHeight="1">
-      <c r="A116" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A116" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B116" s="6" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、認知症施策推進計画の位置づけと見込量への反映、サービス見込量の算定_第1次概算、資料を受領できない場合のサービス見込量、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、アンケート調査の分析_令和8年9月業務報告、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、内部確認結果への対応整理、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、入力前段支援アプリの点検、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D116" s="20" t="n"/>
@@ -5520,17 +5568,17 @@
       <c r="I116" s="21" t="n"/>
     </row>
     <row r="117" ht="32" customHeight="1">
-      <c r="A117" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A117" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、所得段階別第1号被保険者数の将来推計、見える化_見込量の入力値（暫定）、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D117" s="20" t="n"/>
@@ -5541,17 +5589,17 @@
       <c r="I117" s="21" t="n"/>
     </row>
     <row r="118" ht="32" customHeight="1">
-      <c r="A118" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B118" s="6" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、町別データシート、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、見える化データの受領点検_福祉用具住宅改修とリハ、趨勢に現れない要因の分析、見える化_将来推計の設定資料の受領点検、地域ケア会議_受領点検とKPI設計案、認知症施策推進計画の位置づけと見込量への反映、サービス見込量の算定_第1次概算、サービス見込量の算定、サービス見込量の算定_第2次概算、資料を受領できない場合のサービス見込量、サービス見込量算定_統合報告書、対計画比の偏りの補正試算、見込量の季節性の検証と施策反映の設計、サービス見込量の算定_基準年度とパターンの比較、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査結果と年報実績の突合クロス集計、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、アンケート調査の分析_令和8年9月業務報告、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D118" s="20" t="n"/>
@@ -5562,17 +5610,17 @@
       <c r="I118" s="21" t="n"/>
     </row>
     <row r="119" ht="32" customHeight="1">
-      <c r="A119" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A119" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B119" s="6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、見える化_令和8年度実績見込み値の入力案、所得段階別第1号被保険者数の将来推計、見える化_見込量の入力値（暫定）、介護保険事業計画_サービス見込量算定の手引き、地域密着型サービス基準省令の論点整理、給付適正化計画の位置づけと追加検討事項、ケアプラン点検実施要領（案）、基金条例の確認、管理の統合と成果品の棚卸し、計画素案の課題整理、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D119" s="20" t="n"/>
@@ -5582,18 +5630,18 @@
       <c r="H119" s="20" t="n"/>
       <c r="I119" s="21" t="n"/>
     </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B120" s="22" t="n">
-        <v>104</v>
-      </c>
-      <c r="C120" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの99件、別スコープ5件</t>
+    <row r="120" ht="32" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、構成町の意見への回答と工程の前倒し案、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D120" s="20" t="n"/>
@@ -5603,8 +5651,50 @@
       <c r="H120" s="20" t="n"/>
       <c r="I120" s="21" t="n"/>
     </row>
-    <row r="122" ht="100" customHeight="1">
-      <c r="A122" s="23" t="inlineStr">
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+        </is>
+      </c>
+      <c r="D121" s="20" t="n"/>
+      <c r="E121" s="20" t="n"/>
+      <c r="F121" s="20" t="n"/>
+      <c r="G121" s="20" t="n"/>
+      <c r="H121" s="20" t="n"/>
+      <c r="I121" s="21" t="n"/>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B122" s="22" t="n">
+        <v>106</v>
+      </c>
+      <c r="C122" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの101件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D122" s="20" t="n"/>
+      <c r="E122" s="20" t="n"/>
+      <c r="F122" s="20" t="n"/>
+      <c r="G122" s="20" t="n"/>
+      <c r="H122" s="20" t="n"/>
+      <c r="I122" s="21" t="n"/>
+    </row>
+    <row r="124" ht="100" customHeight="1">
+      <c r="A124" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -5612,16 +5702,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A112:I112"/>
     <mergeCell ref="C119:I119"/>
-    <mergeCell ref="A122:H122"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A124:H124"/>
     <mergeCell ref="C118:I118"/>
     <mergeCell ref="C114:I114"/>
-    <mergeCell ref="C113:I113"/>
-    <mergeCell ref="A110:I110"/>
+    <mergeCell ref="C122:I122"/>
     <mergeCell ref="C115:I115"/>
-    <mergeCell ref="C112:I112"/>
     <mergeCell ref="C120:I120"/>
+    <mergeCell ref="C121:I121"/>
     <mergeCell ref="C116:I116"/>
     <mergeCell ref="C117:I117"/>
   </mergeCells>
@@ -5993,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（928段落143表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（951段落146表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1410,7 +1410,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>47 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（951段落146表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（973段落148表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>951段落 146表</t>
+          <t>973段落 148表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>58 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>38 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（951段落146表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（973段落148表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>44 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>151 KB</t>
+          <t>152 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>152 KB</t>
+          <t>153 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（973段落148表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1000段落151表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>973段落 148表</t>
+          <t>1000段落 151表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>153 KB</t>
+          <t>155 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>38 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（973段落148表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1000段落151表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1000段落151表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1001段落151表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1000段落 151表</t>
+          <t>1001段落 151表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>80段落 27表</t>
+          <t>81段落 27表</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>58 KB</t>
+          <t>60 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>155 KB</t>
+          <t>156 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1000段落151表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1001段落151表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1001段落151表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1006段落151表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1001段落 151表</t>
+          <t>1006段落 151表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1001段落151表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1006段落151表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1006段落151表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1019段落152表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1006段落 151表</t>
+          <t>1019段落 152表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1006段落151表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1019段落152表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>60 KB</t>
+          <t>71 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1019段落152表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1024段落152表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1019段落 152表</t>
+          <t>1024段落 152表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>44 KB</t>
+          <t>45 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>156 KB</t>
+          <t>160 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>47 KB</t>
+          <t>48 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1019段落152表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1024段落152表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1024段落152表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1027段落153表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1024段落 152表</t>
+          <t>1027段落 153表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>160 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>48 KB</t>
+          <t>49 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1024段落152表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1027段落153表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1027段落153表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1030段落153表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1027段落 153表</t>
+          <t>1030段落 153表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>45 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>163 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1027段落153表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1030段落153表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1030段落153表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1038段落153表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1030段落 153表</t>
+          <t>1038段落 153表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>49 KB</t>
+          <t>51 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1030段落153表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1038段落153表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1038段落153表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1060段落156表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1038段落 153表</t>
+          <t>1060段落 156表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>77 KB</t>
+          <t>78 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>163 KB</t>
+          <t>166 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>51 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1038段落153表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1060段落156表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1060段落156表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1059段落156表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1060段落 156表</t>
+          <t>1059段落 156表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>47 KB</t>
+          <t>48 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>166 KB</t>
+          <t>170 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1060段落156表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1059段落156表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1059段落156表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1062段落156表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1059段落 156表</t>
+          <t>1062段落 156表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>48 KB</t>
+          <t>49 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>170 KB</t>
+          <t>173 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1059段落156表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1062段落156表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>173 KB</t>
+          <t>174 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>71 KB</t>
+          <t>72 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>174 KB</t>
+          <t>175 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -6114,17 +6114,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画書は上記。概要版は未着手。</t>
+          <t>計画書は上記。概要版は第10期介護保険事業計画_概要版.docx（A4判8頁）。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>概要版の頁数、体裁、掲載内容。</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>概要版の頁数と判型、体裁、保険料の掲載の範囲、2版構成の可否。いずれも別冊「概要版の構成案」07シートの決定を要する事項6件によるため、受託者の案によっている。</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>175 KB</t>
+          <t>179 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1062段落156表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1063段落156表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1062段落 156表</t>
+          <t>1063段落 156表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>179 KB</t>
+          <t>180 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>26 KB</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1062段落156表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1063段落156表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>180 KB</t>
+          <t>185 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1063段落156表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1074段落158表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1063段落 156表</t>
+          <t>1074段落 158表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>49 KB</t>
+          <t>51 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>185 KB</t>
+          <t>190 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1063段落156表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1074段落158表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>190 KB</t>
+          <t>195 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1074段落158表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1083段落160表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1074段落 158表</t>
+          <t>1083段落 160表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>78 KB</t>
+          <t>79 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>195 KB</t>
+          <t>198 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1074段落158表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1083段落160表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -770,17 +770,17 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1083段落160表36図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（1090段落161表36図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1083段落 160表</t>
+          <t>1090段落 161表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2.6 MB</t>
+          <t>2.7 MB</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した（確認事項No.156）。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数0.991352と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準13段階とは異なるため、入力画面では所得段階の設定を弾力化とする。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する。自己点検12件はいずれも適合している。</t>
+          <t>見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した（確認事項No.156）。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数0.991352と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が156円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準13段階とは異なるため、入力画面では所得段階の設定を弾力化とする。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する。自己点検12件はいずれも適合している。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>79 KB</t>
+          <t>82 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>198 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>56 KB</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1083段落160表36図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（1090段落161表36図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
